--- a/data/obx_xlsx/AZT.OL.xlsx
+++ b/data/obx_xlsx/AZT.OL.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="378">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -252,13 +252,16 @@
     <t>Other Operaiting Income</t>
   </si>
   <si>
+    <t>Cost of materials old</t>
+  </si>
+  <si>
+    <t>Change in inventory</t>
+  </si>
+  <si>
+    <t>Cost of goods</t>
+  </si>
+  <si>
     <t>Cost of materials</t>
-  </si>
-  <si>
-    <t>Change in inventory</t>
-  </si>
-  <si>
-    <t>Cost of goods</t>
   </si>
   <si>
     <t>Personnel Expenses</t>
@@ -1275,7 +1278,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1338,6 +1341,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -2512,7 +2518,7 @@
       <c r="W25" s="20"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="21" t="s">
         <v>77</v>
       </c>
       <c r="B26" s="20"/>
@@ -2664,7 +2670,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B29" s="15">
         <v>4.36</v>
@@ -2701,7 +2707,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B30" s="15">
         <v>67.94</v>
@@ -2772,7 +2778,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B31" s="15">
         <v>9.15</v>
@@ -2843,7 +2849,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B32" s="15">
         <v>2.28</v>
@@ -2898,7 +2904,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="15">
@@ -2931,7 +2937,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B34" s="15">
         <v>2.56</v>
@@ -2986,7 +2992,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B35" s="15">
         <v>4.31</v>
@@ -3029,7 +3035,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B36" s="20"/>
       <c r="C36" s="20"/>
@@ -3044,7 +3050,7 @@
       <c r="H36" s="19">
         <v>-2.54</v>
       </c>
-      <c r="I36" s="21">
+      <c r="I36" s="22">
         <v>0.0</v>
       </c>
       <c r="J36" s="20"/>
@@ -3064,7 +3070,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="20"/>
@@ -3077,11 +3083,11 @@
       <c r="H37" s="20"/>
       <c r="I37" s="20"/>
       <c r="J37" s="20"/>
-      <c r="K37" s="21">
+      <c r="K37" s="22">
         <v>0.0</v>
       </c>
       <c r="L37" s="20"/>
-      <c r="M37" s="21">
+      <c r="M37" s="22">
         <v>0.0</v>
       </c>
       <c r="N37" s="20"/>
@@ -3097,7 +3103,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
@@ -3138,7 +3144,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B39" s="15">
         <v>33.62</v>
@@ -3209,7 +3215,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B40" s="20"/>
       <c r="C40" s="20"/>
@@ -3250,7 +3256,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B41" s="20"/>
       <c r="C41" s="15">
@@ -3301,7 +3307,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="15">
@@ -3340,7 +3346,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B43" s="20"/>
       <c r="C43" s="15">
@@ -3391,7 +3397,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="15">
@@ -3417,7 +3423,7 @@
       </c>
       <c r="J44" s="20"/>
       <c r="K44" s="20"/>
-      <c r="L44" s="21">
+      <c r="L44" s="22">
         <v>0.0</v>
       </c>
       <c r="M44" s="19">
@@ -3440,7 +3446,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B45" s="17">
         <v>109.81</v>
@@ -3511,23 +3517,23 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B46" s="20">
         <v>0.0</v>
       </c>
-      <c r="C46" s="21">
+      <c r="C46" s="22">
         <v>0.0</v>
       </c>
       <c r="D46" s="20"/>
-      <c r="E46" s="21">
-        <v>0.0</v>
-      </c>
-      <c r="F46" s="21">
+      <c r="E46" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="F46" s="22">
         <v>0.0</v>
       </c>
       <c r="G46" s="20"/>
-      <c r="H46" s="21">
+      <c r="H46" s="22">
         <v>0.0</v>
       </c>
       <c r="I46" s="20"/>
@@ -3550,12 +3556,12 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B47" s="18">
         <v>2.81</v>
       </c>
-      <c r="C47" s="22">
+      <c r="C47" s="23">
         <v>-1.44</v>
       </c>
       <c r="D47" s="18">
@@ -3570,58 +3576,58 @@
       <c r="G47" s="18">
         <v>42.79</v>
       </c>
-      <c r="H47" s="22">
+      <c r="H47" s="23">
         <v>-0.41</v>
       </c>
-      <c r="I47" s="22">
+      <c r="I47" s="23">
         <v>-13.51</v>
       </c>
-      <c r="J47" s="22">
+      <c r="J47" s="23">
         <v>-24.91</v>
       </c>
-      <c r="K47" s="22">
+      <c r="K47" s="23">
         <v>-20.96</v>
       </c>
-      <c r="L47" s="22">
+      <c r="L47" s="23">
         <v>-17.31</v>
       </c>
-      <c r="M47" s="22">
+      <c r="M47" s="23">
         <v>-23.63</v>
       </c>
-      <c r="N47" s="22">
+      <c r="N47" s="23">
         <v>-23.81</v>
       </c>
-      <c r="O47" s="22">
+      <c r="O47" s="23">
         <v>-24.73</v>
       </c>
-      <c r="P47" s="22">
+      <c r="P47" s="23">
         <v>-21.19</v>
       </c>
-      <c r="Q47" s="22">
+      <c r="Q47" s="23">
         <v>-29.28</v>
       </c>
-      <c r="R47" s="22">
+      <c r="R47" s="23">
         <v>-85.12</v>
       </c>
-      <c r="S47" s="22">
+      <c r="S47" s="23">
         <v>-91.31</v>
       </c>
-      <c r="T47" s="22">
+      <c r="T47" s="23">
         <v>-39.3</v>
       </c>
-      <c r="U47" s="22">
+      <c r="U47" s="23">
         <v>-40.15</v>
       </c>
-      <c r="V47" s="22">
+      <c r="V47" s="23">
         <v>-16.01</v>
       </c>
-      <c r="W47" s="22">
+      <c r="W47" s="23">
         <v>-9.33</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B48" s="15">
         <v>9.37</v>
@@ -3652,7 +3658,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B49" s="20"/>
       <c r="C49" s="15">
@@ -3711,7 +3717,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="15">
@@ -3762,7 +3768,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="15">
@@ -3793,7 +3799,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B52" s="20"/>
       <c r="C52" s="15">
@@ -3834,7 +3840,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B53" s="20"/>
       <c r="C53" s="20"/>
@@ -3873,14 +3879,14 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="20">
         <v>0.0</v>
       </c>
       <c r="D54" s="20"/>
-      <c r="E54" s="21">
+      <c r="E54" s="22">
         <v>0.0</v>
       </c>
       <c r="F54" s="20"/>
@@ -3904,7 +3910,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B55" s="20"/>
       <c r="C55" s="20"/>
@@ -3935,7 +3941,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B56" s="20"/>
       <c r="C56" s="19">
@@ -3971,7 +3977,7 @@
       <c r="M56" s="20">
         <v>0.0</v>
       </c>
-      <c r="N56" s="21">
+      <c r="N56" s="22">
         <v>0.0</v>
       </c>
       <c r="O56" s="19">
@@ -3996,7 +4002,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B57" s="20"/>
       <c r="C57" s="20"/>
@@ -4035,7 +4041,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B58" s="20"/>
       <c r="C58" s="19">
@@ -4074,7 +4080,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B59" s="20"/>
       <c r="C59" s="20"/>
@@ -4105,7 +4111,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B60" s="20"/>
       <c r="C60" s="20"/>
@@ -4134,7 +4140,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
@@ -4148,7 +4154,7 @@
       <c r="K61" s="20"/>
       <c r="L61" s="20"/>
       <c r="M61" s="20"/>
-      <c r="N61" s="21">
+      <c r="N61" s="22">
         <v>0.0</v>
       </c>
       <c r="O61" s="19">
@@ -4165,9 +4171,9 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="B62" s="21">
+        <v>113</v>
+      </c>
+      <c r="B62" s="22">
         <v>0.0</v>
       </c>
       <c r="C62" s="20"/>
@@ -4204,7 +4210,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B63" s="18">
         <v>9.37</v>
@@ -4221,13 +4227,13 @@
       <c r="F63" s="18">
         <v>0.57</v>
       </c>
-      <c r="G63" s="22">
+      <c r="G63" s="23">
         <v>-0.38</v>
       </c>
-      <c r="H63" s="22">
+      <c r="H63" s="23">
         <v>-0.16</v>
       </c>
-      <c r="I63" s="22">
+      <c r="I63" s="23">
         <v>-0.53</v>
       </c>
       <c r="J63" s="18">
@@ -4275,7 +4281,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B64" s="18">
         <v>12.18</v>
@@ -4295,58 +4301,58 @@
       <c r="G64" s="18">
         <v>42.41</v>
       </c>
-      <c r="H64" s="22">
+      <c r="H64" s="23">
         <v>-0.57</v>
       </c>
-      <c r="I64" s="22">
+      <c r="I64" s="23">
         <v>-14.03</v>
       </c>
-      <c r="J64" s="22">
+      <c r="J64" s="23">
         <v>-24.8</v>
       </c>
-      <c r="K64" s="22">
+      <c r="K64" s="23">
         <v>-20.39</v>
       </c>
-      <c r="L64" s="22">
+      <c r="L64" s="23">
         <v>-17.29</v>
       </c>
-      <c r="M64" s="22">
+      <c r="M64" s="23">
         <v>-21.99</v>
       </c>
-      <c r="N64" s="22">
+      <c r="N64" s="23">
         <v>-22.89</v>
       </c>
-      <c r="O64" s="22">
+      <c r="O64" s="23">
         <v>-24.32</v>
       </c>
-      <c r="P64" s="22">
+      <c r="P64" s="23">
         <v>-20.1</v>
       </c>
-      <c r="Q64" s="22">
+      <c r="Q64" s="23">
         <v>-28.54</v>
       </c>
-      <c r="R64" s="22">
+      <c r="R64" s="23">
         <v>-81.21</v>
       </c>
-      <c r="S64" s="22">
+      <c r="S64" s="23">
         <v>-82.99</v>
       </c>
-      <c r="T64" s="22">
+      <c r="T64" s="23">
         <v>-34.06</v>
       </c>
-      <c r="U64" s="22">
+      <c r="U64" s="23">
         <v>-37.94</v>
       </c>
-      <c r="V64" s="22">
+      <c r="V64" s="23">
         <v>-15.45</v>
       </c>
-      <c r="W64" s="22">
+      <c r="W64" s="23">
         <v>-8.92</v>
       </c>
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B65" s="15">
         <v>2.3</v>
@@ -4415,7 +4421,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="15">
@@ -4452,7 +4458,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
@@ -4485,7 +4491,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
@@ -4518,7 +4524,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
@@ -4551,7 +4557,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
@@ -4580,7 +4586,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B71" s="18">
         <v>2.3</v>
@@ -4597,59 +4603,59 @@
       <c r="F71" s="18">
         <v>12.62</v>
       </c>
-      <c r="G71" s="22">
+      <c r="G71" s="23">
         <v>-33.14</v>
       </c>
-      <c r="H71" s="23"/>
-      <c r="I71" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="J71" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="K71" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="L71" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="M71" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="N71" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="O71" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="P71" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="Q71" s="23">
+      <c r="H71" s="24"/>
+      <c r="I71" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="J71" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="K71" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="L71" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="M71" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="N71" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="O71" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="P71" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="Q71" s="24">
         <v>0.0</v>
       </c>
       <c r="R71" s="18">
         <v>30.71</v>
       </c>
-      <c r="S71" s="22">
+      <c r="S71" s="23">
         <v>-4.19</v>
       </c>
-      <c r="T71" s="22">
+      <c r="T71" s="23">
         <v>-10.89</v>
       </c>
-      <c r="U71" s="22">
+      <c r="U71" s="23">
         <v>-11.28</v>
       </c>
-      <c r="V71" s="22">
+      <c r="V71" s="23">
         <v>-3.63</v>
       </c>
-      <c r="W71" s="22">
+      <c r="W71" s="23">
         <v>-2.56</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B72" s="18">
         <v>9.88</v>
@@ -4669,58 +4675,58 @@
       <c r="G72" s="18">
         <v>75.55</v>
       </c>
-      <c r="H72" s="22">
+      <c r="H72" s="23">
         <v>-0.57</v>
       </c>
-      <c r="I72" s="22">
+      <c r="I72" s="23">
         <v>-14.03</v>
       </c>
-      <c r="J72" s="22">
+      <c r="J72" s="23">
         <v>-24.8</v>
       </c>
-      <c r="K72" s="22">
+      <c r="K72" s="23">
         <v>-20.39</v>
       </c>
-      <c r="L72" s="22">
+      <c r="L72" s="23">
         <v>-17.29</v>
       </c>
-      <c r="M72" s="22">
+      <c r="M72" s="23">
         <v>-21.99</v>
       </c>
-      <c r="N72" s="22">
+      <c r="N72" s="23">
         <v>-22.89</v>
       </c>
-      <c r="O72" s="22">
+      <c r="O72" s="23">
         <v>-24.32</v>
       </c>
-      <c r="P72" s="22">
+      <c r="P72" s="23">
         <v>-20.1</v>
       </c>
-      <c r="Q72" s="22">
+      <c r="Q72" s="23">
         <v>-28.54</v>
       </c>
-      <c r="R72" s="24">
+      <c r="R72" s="25">
         <v>-111.92</v>
       </c>
-      <c r="S72" s="22">
+      <c r="S72" s="23">
         <v>-78.8</v>
       </c>
-      <c r="T72" s="22">
+      <c r="T72" s="23">
         <v>-23.17</v>
       </c>
-      <c r="U72" s="22">
+      <c r="U72" s="23">
         <v>-26.65</v>
       </c>
-      <c r="V72" s="22">
+      <c r="V72" s="23">
         <v>-11.81</v>
       </c>
-      <c r="W72" s="22">
+      <c r="W72" s="23">
         <v>-6.36</v>
       </c>
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B73" s="20"/>
       <c r="C73" s="20">
@@ -4730,7 +4736,7 @@
       <c r="E73" s="20">
         <v>0.0</v>
       </c>
-      <c r="F73" s="21">
+      <c r="F73" s="22">
         <v>0.0</v>
       </c>
       <c r="G73" s="20"/>
@@ -4753,7 +4759,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B74" s="18">
         <v>9.88</v>
@@ -4773,58 +4779,58 @@
       <c r="G74" s="18">
         <v>75.55</v>
       </c>
-      <c r="H74" s="22">
+      <c r="H74" s="23">
         <v>-0.57</v>
       </c>
-      <c r="I74" s="22">
+      <c r="I74" s="23">
         <v>-14.03</v>
       </c>
-      <c r="J74" s="22">
+      <c r="J74" s="23">
         <v>-24.8</v>
       </c>
-      <c r="K74" s="22">
+      <c r="K74" s="23">
         <v>-20.39</v>
       </c>
-      <c r="L74" s="22">
+      <c r="L74" s="23">
         <v>-17.29</v>
       </c>
-      <c r="M74" s="22">
+      <c r="M74" s="23">
         <v>-21.99</v>
       </c>
-      <c r="N74" s="22">
+      <c r="N74" s="23">
         <v>-22.89</v>
       </c>
-      <c r="O74" s="22">
+      <c r="O74" s="23">
         <v>-24.32</v>
       </c>
-      <c r="P74" s="22">
+      <c r="P74" s="23">
         <v>-20.1</v>
       </c>
-      <c r="Q74" s="22">
+      <c r="Q74" s="23">
         <v>-28.54</v>
       </c>
-      <c r="R74" s="24">
+      <c r="R74" s="25">
         <v>-111.92</v>
       </c>
-      <c r="S74" s="22">
+      <c r="S74" s="23">
         <v>-78.8</v>
       </c>
-      <c r="T74" s="22">
+      <c r="T74" s="23">
         <v>-23.17</v>
       </c>
-      <c r="U74" s="22">
+      <c r="U74" s="23">
         <v>-26.65</v>
       </c>
-      <c r="V74" s="22">
+      <c r="V74" s="23">
         <v>-11.81</v>
       </c>
-      <c r="W74" s="22">
+      <c r="W74" s="23">
         <v>-6.36</v>
       </c>
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
@@ -4861,28 +4867,28 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="B76" s="23"/>
-      <c r="C76" s="23"/>
-      <c r="D76" s="23"/>
-      <c r="E76" s="23"/>
-      <c r="F76" s="23"/>
+        <v>125</v>
+      </c>
+      <c r="B76" s="24"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="24"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
       <c r="G76" s="18">
         <v>9.36</v>
       </c>
-      <c r="H76" s="22">
+      <c r="H76" s="23">
         <v>-5.36</v>
       </c>
-      <c r="I76" s="23"/>
-      <c r="J76" s="23"/>
-      <c r="K76" s="23"/>
-      <c r="L76" s="23"/>
-      <c r="M76" s="23"/>
-      <c r="N76" s="23"/>
-      <c r="O76" s="23"/>
-      <c r="P76" s="23"/>
-      <c r="Q76" s="23"/>
+      <c r="I76" s="24"/>
+      <c r="J76" s="24"/>
+      <c r="K76" s="24"/>
+      <c r="L76" s="24"/>
+      <c r="M76" s="24"/>
+      <c r="N76" s="24"/>
+      <c r="O76" s="24"/>
+      <c r="P76" s="24"/>
+      <c r="Q76" s="24"/>
       <c r="R76" s="18">
         <v>12.55</v>
       </c>
@@ -4892,13 +4898,13 @@
       <c r="T76" s="18">
         <v>4.51</v>
       </c>
-      <c r="U76" s="23"/>
-      <c r="V76" s="23"/>
-      <c r="W76" s="23"/>
+      <c r="U76" s="24"/>
+      <c r="V76" s="24"/>
+      <c r="W76" s="24"/>
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B77" s="18">
         <v>9.88</v>
@@ -4918,58 +4924,58 @@
       <c r="G77" s="18">
         <v>83.12</v>
       </c>
-      <c r="H77" s="22">
+      <c r="H77" s="23">
         <v>-6.39</v>
       </c>
-      <c r="I77" s="22">
+      <c r="I77" s="23">
         <v>-14.19</v>
       </c>
-      <c r="J77" s="22">
+      <c r="J77" s="23">
         <v>-24.94</v>
       </c>
-      <c r="K77" s="22">
+      <c r="K77" s="23">
         <v>-20.48</v>
       </c>
-      <c r="L77" s="22">
+      <c r="L77" s="23">
         <v>-17.34</v>
       </c>
-      <c r="M77" s="22">
+      <c r="M77" s="23">
         <v>-21.99</v>
       </c>
-      <c r="N77" s="22">
+      <c r="N77" s="23">
         <v>-22.89</v>
       </c>
-      <c r="O77" s="22">
+      <c r="O77" s="23">
         <v>-24.32</v>
       </c>
-      <c r="P77" s="22">
+      <c r="P77" s="23">
         <v>-20.1</v>
       </c>
-      <c r="Q77" s="22">
+      <c r="Q77" s="23">
         <v>-28.54</v>
       </c>
-      <c r="R77" s="22">
+      <c r="R77" s="23">
         <v>-99.37</v>
       </c>
-      <c r="S77" s="22">
+      <c r="S77" s="23">
         <v>-52.18</v>
       </c>
-      <c r="T77" s="22">
+      <c r="T77" s="23">
         <v>-18.66</v>
       </c>
-      <c r="U77" s="22">
+      <c r="U77" s="23">
         <v>-26.65</v>
       </c>
-      <c r="V77" s="22">
+      <c r="V77" s="23">
         <v>-11.81</v>
       </c>
-      <c r="W77" s="22">
+      <c r="W77" s="23">
         <v>-6.36</v>
       </c>
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
@@ -5010,13 +5016,13 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="B79" s="23"/>
-      <c r="C79" s="23"/>
-      <c r="D79" s="23"/>
-      <c r="E79" s="23"/>
-      <c r="F79" s="23">
+        <v>127</v>
+      </c>
+      <c r="B79" s="24"/>
+      <c r="C79" s="24"/>
+      <c r="D79" s="24"/>
+      <c r="E79" s="24"/>
+      <c r="F79" s="24">
         <v>0.0</v>
       </c>
       <c r="G79" s="18">
@@ -5037,21 +5043,21 @@
       <c r="L79" s="18">
         <v>0.05</v>
       </c>
-      <c r="M79" s="23"/>
-      <c r="N79" s="23"/>
-      <c r="O79" s="23"/>
-      <c r="P79" s="23"/>
-      <c r="Q79" s="23"/>
-      <c r="R79" s="23"/>
-      <c r="S79" s="23"/>
-      <c r="T79" s="23"/>
-      <c r="U79" s="23"/>
-      <c r="V79" s="23"/>
-      <c r="W79" s="23"/>
+      <c r="M79" s="24"/>
+      <c r="N79" s="24"/>
+      <c r="O79" s="24"/>
+      <c r="P79" s="24"/>
+      <c r="Q79" s="24"/>
+      <c r="R79" s="24"/>
+      <c r="S79" s="24"/>
+      <c r="T79" s="24"/>
+      <c r="U79" s="24"/>
+      <c r="V79" s="24"/>
+      <c r="W79" s="24"/>
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B80" s="18">
         <v>9.88</v>
@@ -5071,58 +5077,58 @@
       <c r="G80" s="18">
         <v>73.76</v>
       </c>
-      <c r="H80" s="22">
+      <c r="H80" s="23">
         <v>-1.03</v>
       </c>
-      <c r="I80" s="22">
+      <c r="I80" s="23">
         <v>-14.19</v>
       </c>
-      <c r="J80" s="22">
+      <c r="J80" s="23">
         <v>-24.94</v>
       </c>
-      <c r="K80" s="22">
+      <c r="K80" s="23">
         <v>-20.48</v>
       </c>
-      <c r="L80" s="22">
+      <c r="L80" s="23">
         <v>-17.34</v>
       </c>
-      <c r="M80" s="22">
+      <c r="M80" s="23">
         <v>-21.99</v>
       </c>
-      <c r="N80" s="22">
+      <c r="N80" s="23">
         <v>-22.89</v>
       </c>
-      <c r="O80" s="22">
+      <c r="O80" s="23">
         <v>-24.32</v>
       </c>
-      <c r="P80" s="22">
+      <c r="P80" s="23">
         <v>-20.1</v>
       </c>
-      <c r="Q80" s="22">
+      <c r="Q80" s="23">
         <v>-28.54</v>
       </c>
-      <c r="R80" s="24">
+      <c r="R80" s="25">
         <v>-111.92</v>
       </c>
-      <c r="S80" s="22">
+      <c r="S80" s="23">
         <v>-78.8</v>
       </c>
-      <c r="T80" s="22">
+      <c r="T80" s="23">
         <v>-23.17</v>
       </c>
-      <c r="U80" s="22">
+      <c r="U80" s="23">
         <v>-26.65</v>
       </c>
-      <c r="V80" s="22">
+      <c r="V80" s="23">
         <v>-11.81</v>
       </c>
-      <c r="W80" s="22">
+      <c r="W80" s="23">
         <v>-6.36</v>
       </c>
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B81" s="20">
         <v>0.0</v>
@@ -5151,7 +5157,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B82" s="18">
         <v>9.88</v>
@@ -5171,58 +5177,58 @@
       <c r="G82" s="18">
         <v>83.12</v>
       </c>
-      <c r="H82" s="22">
+      <c r="H82" s="23">
         <v>-6.39</v>
       </c>
-      <c r="I82" s="22">
+      <c r="I82" s="23">
         <v>-14.19</v>
       </c>
-      <c r="J82" s="22">
+      <c r="J82" s="23">
         <v>-24.94</v>
       </c>
-      <c r="K82" s="22">
+      <c r="K82" s="23">
         <v>-20.48</v>
       </c>
-      <c r="L82" s="22">
+      <c r="L82" s="23">
         <v>-17.34</v>
       </c>
-      <c r="M82" s="22">
+      <c r="M82" s="23">
         <v>-21.99</v>
       </c>
-      <c r="N82" s="22">
+      <c r="N82" s="23">
         <v>-22.89</v>
       </c>
-      <c r="O82" s="22">
+      <c r="O82" s="23">
         <v>-24.32</v>
       </c>
-      <c r="P82" s="22">
+      <c r="P82" s="23">
         <v>-20.1</v>
       </c>
-      <c r="Q82" s="22">
+      <c r="Q82" s="23">
         <v>-28.54</v>
       </c>
-      <c r="R82" s="22">
+      <c r="R82" s="23">
         <v>-99.37</v>
       </c>
-      <c r="S82" s="22">
+      <c r="S82" s="23">
         <v>-52.18</v>
       </c>
-      <c r="T82" s="22">
+      <c r="T82" s="23">
         <v>-18.66</v>
       </c>
-      <c r="U82" s="22">
+      <c r="U82" s="23">
         <v>-26.65</v>
       </c>
-      <c r="V82" s="22">
+      <c r="V82" s="23">
         <v>-11.81</v>
       </c>
-      <c r="W82" s="22">
+      <c r="W82" s="23">
         <v>-6.36</v>
       </c>
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B83" s="15">
         <v>50.2</v>
@@ -5293,7 +5299,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B84" s="15">
         <v>50.2</v>
@@ -5364,7 +5370,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B85" s="15">
         <v>0.19</v>
@@ -5435,7 +5441,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B86" s="15">
         <v>0.2</v>
@@ -5506,7 +5512,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B87" s="15">
         <v>0.19</v>
@@ -5577,7 +5583,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B88" s="15">
         <v>0.2</v>
@@ -5648,7 +5654,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B89" s="15">
         <v>9.88</v>
@@ -5719,7 +5725,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B90" s="15">
         <v>9.88</v>
@@ -5769,7 +5775,7 @@
       <c r="Q90" s="19">
         <v>-28.54</v>
       </c>
-      <c r="R90" s="25">
+      <c r="R90" s="26">
         <v>-111.92</v>
       </c>
       <c r="S90" s="19">
@@ -5790,7 +5796,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B91" s="20"/>
       <c r="C91" s="20"/>
@@ -5825,7 +5831,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B92" s="20"/>
       <c r="C92" s="20"/>
@@ -5868,7 +5874,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B93" s="20"/>
       <c r="C93" s="20"/>
@@ -5905,7 +5911,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B94" s="20"/>
       <c r="C94" s="15">
@@ -5960,7 +5966,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B95" s="20"/>
       <c r="C95" s="15">
@@ -6017,7 +6023,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B96" s="20"/>
       <c r="C96" s="15">
@@ -6074,7 +6080,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B97" s="20"/>
       <c r="C97" s="20"/>
@@ -6127,7 +6133,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B98" s="20"/>
       <c r="C98" s="15">
@@ -6182,7 +6188,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B99" s="20"/>
       <c r="C99" s="20"/>
@@ -6225,7 +6231,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B100" s="20"/>
       <c r="C100" s="20"/>
@@ -6239,7 +6245,7 @@
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
       <c r="M100" s="20"/>
-      <c r="N100" s="21">
+      <c r="N100" s="22">
         <v>0.0</v>
       </c>
       <c r="O100" s="20"/>
@@ -6254,7 +6260,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B101" s="20"/>
       <c r="C101" s="20"/>
@@ -6291,7 +6297,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B102" s="15">
         <v>6.59</v>
@@ -6362,7 +6368,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B103" s="15">
         <v>2.56</v>
@@ -6417,7 +6423,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B104" s="15">
         <v>9.15</v>
@@ -6488,7 +6494,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B105" s="20"/>
       <c r="C105" s="20"/>
@@ -6527,7 +6533,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B106" s="20"/>
       <c r="C106" s="20"/>
@@ -6560,7 +6566,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B107" s="15">
         <v>50.2</v>
@@ -6615,7 +6621,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B108" s="15">
         <v>50.2</v>
@@ -6670,7 +6676,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B109" s="15">
         <v>0.19</v>
@@ -6725,7 +6731,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B110" s="15">
         <v>0.19</v>
@@ -6780,7 +6786,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B111" s="15">
         <v>0.2</v>
@@ -6835,7 +6841,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B112" s="15">
         <v>0.2</v>
@@ -6890,7 +6896,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B113" s="15">
         <v>9.88</v>
@@ -6945,7 +6951,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B114" s="15">
         <v>9.88</v>
@@ -7000,7 +7006,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B115" s="15">
         <v>9.88</v>
@@ -7055,7 +7061,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B116" s="15">
         <v>9.88</v>
@@ -7110,7 +7116,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B117" s="15">
         <v>1.0</v>
@@ -7165,7 +7171,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B118" s="15">
         <v>1.0</v>
@@ -8121,7 +8127,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8507,75 +8513,75 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -8673,7 +8679,7 @@
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B19" s="15">
         <v>16.16</v>
@@ -8728,7 +8734,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="15">
@@ -8793,7 +8799,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="15">
@@ -8828,7 +8834,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="15">
@@ -8893,10 +8899,10 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B23" s="20"/>
-      <c r="C23" s="21">
+      <c r="C23" s="22">
         <v>0.0</v>
       </c>
       <c r="D23" s="20">
@@ -8904,11 +8910,11 @@
       </c>
       <c r="E23" s="20"/>
       <c r="F23" s="20"/>
-      <c r="G23" s="21">
+      <c r="G23" s="22">
         <v>0.0</v>
       </c>
       <c r="H23" s="20"/>
-      <c r="I23" s="21">
+      <c r="I23" s="22">
         <v>0.0</v>
       </c>
       <c r="J23" s="20"/>
@@ -8916,7 +8922,7 @@
         <v>0.0</v>
       </c>
       <c r="L23" s="20"/>
-      <c r="M23" s="21">
+      <c r="M23" s="22">
         <v>0.0</v>
       </c>
       <c r="N23" s="20"/>
@@ -8932,7 +8938,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
@@ -8987,7 +8993,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B25" s="14">
         <v>103.91</v>
@@ -9016,7 +9022,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="15">
@@ -9071,7 +9077,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
@@ -9114,7 +9120,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
@@ -9173,7 +9179,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="20"/>
@@ -9232,7 +9238,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
@@ -9293,7 +9299,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -9322,7 +9328,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="15">
@@ -9353,7 +9359,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="15">
@@ -9386,7 +9392,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="15">
@@ -9419,7 +9425,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="15">
@@ -9450,7 +9456,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B36" s="14">
         <v>187.78</v>
@@ -9521,10 +9527,10 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B37" s="20"/>
-      <c r="C37" s="21">
+      <c r="C37" s="22">
         <v>0.0</v>
       </c>
       <c r="D37" s="20">
@@ -9534,14 +9540,14 @@
         <v>0.0</v>
       </c>
       <c r="F37" s="20"/>
-      <c r="G37" s="21">
-        <v>0.0</v>
-      </c>
-      <c r="H37" s="21">
+      <c r="G37" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="H37" s="22">
         <v>0.0</v>
       </c>
       <c r="I37" s="20"/>
-      <c r="J37" s="21">
+      <c r="J37" s="22">
         <v>0.0</v>
       </c>
       <c r="K37" s="20"/>
@@ -9560,7 +9566,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B38" s="17">
         <v>307.85</v>
@@ -9631,7 +9637,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B39" s="15">
         <v>11.62</v>
@@ -9710,7 +9716,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B40" s="20"/>
       <c r="C40" s="15">
@@ -9775,7 +9781,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B41" s="20"/>
       <c r="C41" s="19">
@@ -9824,11 +9830,11 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
-      <c r="D42" s="21">
+      <c r="D42" s="22">
         <v>0.0</v>
       </c>
       <c r="E42" s="20"/>
@@ -9842,10 +9848,10 @@
       </c>
       <c r="L42" s="20"/>
       <c r="M42" s="20"/>
-      <c r="N42" s="21">
-        <v>0.0</v>
-      </c>
-      <c r="O42" s="21">
+      <c r="N42" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="O42" s="22">
         <v>0.0</v>
       </c>
       <c r="P42" s="20"/>
@@ -9859,7 +9865,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B43" s="20"/>
       <c r="C43" s="19">
@@ -9894,7 +9900,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="15">
@@ -9929,11 +9935,11 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
-      <c r="D45" s="21">
+      <c r="D45" s="22">
         <v>0.0</v>
       </c>
       <c r="E45" s="20"/>
@@ -9958,7 +9964,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
@@ -10017,7 +10023,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
@@ -10060,24 +10066,24 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
       <c r="D48" s="20"/>
       <c r="E48" s="20"/>
       <c r="F48" s="20"/>
-      <c r="G48" s="21">
+      <c r="G48" s="22">
         <v>0.0</v>
       </c>
       <c r="H48" s="20"/>
-      <c r="I48" s="21">
+      <c r="I48" s="22">
         <v>0.0</v>
       </c>
       <c r="J48" s="20"/>
       <c r="K48" s="20"/>
       <c r="L48" s="20"/>
-      <c r="M48" s="21">
+      <c r="M48" s="22">
         <v>0.0</v>
       </c>
       <c r="N48" s="20"/>
@@ -10093,7 +10099,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B49" s="20"/>
       <c r="C49" s="20">
@@ -10136,7 +10142,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B50" s="15">
         <v>34.06</v>
@@ -10191,7 +10197,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="15">
@@ -10240,16 +10246,16 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B52" s="20"/>
       <c r="C52" s="19">
         <v>-0.45</v>
       </c>
-      <c r="D52" s="21">
-        <v>0.0</v>
-      </c>
-      <c r="E52" s="21">
+      <c r="D52" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="E52" s="22">
         <v>0.0</v>
       </c>
       <c r="F52" s="20"/>
@@ -10281,7 +10287,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B53" s="20"/>
       <c r="C53" s="15">
@@ -10340,7 +10346,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="19">
@@ -10389,7 +10395,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B55" s="20"/>
       <c r="C55" s="20">
@@ -10422,13 +10428,13 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B56" s="20"/>
-      <c r="C56" s="21">
-        <v>0.0</v>
-      </c>
-      <c r="D56" s="21">
+      <c r="C56" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="D56" s="22">
         <v>0.0</v>
       </c>
       <c r="E56" s="20"/>
@@ -10453,7 +10459,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B57" s="20"/>
       <c r="C57" s="20"/>
@@ -10486,7 +10492,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B58" s="20"/>
       <c r="C58" s="20"/>
@@ -10533,7 +10539,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B59" s="15">
         <v>5.15</v>
@@ -10576,7 +10582,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B60" s="20"/>
       <c r="C60" s="15">
@@ -10617,7 +10623,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="19">
@@ -10658,7 +10664,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B62" s="20"/>
       <c r="C62" s="20"/>
@@ -10672,7 +10678,7 @@
       <c r="G62" s="20">
         <v>0.0</v>
       </c>
-      <c r="H62" s="21">
+      <c r="H62" s="22">
         <v>0.0</v>
       </c>
       <c r="I62" s="20"/>
@@ -10693,7 +10699,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
@@ -10736,7 +10742,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
@@ -10777,7 +10783,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
@@ -10828,7 +10834,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
@@ -10863,7 +10869,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
@@ -10914,7 +10920,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
@@ -10945,7 +10951,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
@@ -10982,7 +10988,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B70" s="15">
         <v>1.49</v>
@@ -11031,7 +11037,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B71" s="15">
         <v>1.24</v>
@@ -11064,16 +11070,16 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B72" s="20"/>
       <c r="C72" s="20"/>
       <c r="D72" s="20"/>
       <c r="E72" s="20"/>
-      <c r="F72" s="21">
-        <v>0.0</v>
-      </c>
-      <c r="G72" s="21">
+      <c r="F72" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="G72" s="22">
         <v>0.0</v>
       </c>
       <c r="H72" s="20"/>
@@ -11083,7 +11089,7 @@
         <v>0.0</v>
       </c>
       <c r="L72" s="20"/>
-      <c r="M72" s="21">
+      <c r="M72" s="22">
         <v>0.0</v>
       </c>
       <c r="N72" s="20"/>
@@ -11099,7 +11105,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B73" s="18">
         <v>53.56</v>
@@ -11170,7 +11176,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B74" s="20"/>
       <c r="C74" s="20"/>
@@ -11199,15 +11205,15 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
       <c r="D75" s="20"/>
-      <c r="E75" s="21">
-        <v>0.0</v>
-      </c>
-      <c r="F75" s="21">
+      <c r="E75" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="F75" s="22">
         <v>0.0</v>
       </c>
       <c r="G75" s="20">
@@ -11236,7 +11242,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
@@ -11269,7 +11275,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B77" s="17">
         <v>361.41</v>
@@ -11340,7 +11346,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B78" s="15">
         <v>1.19</v>
@@ -11383,7 +11389,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B79" s="15">
         <v>5.0</v>
@@ -11450,7 +11456,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B80" s="20"/>
       <c r="C80" s="20"/>
@@ -11469,7 +11475,7 @@
         <v>0.0</v>
       </c>
       <c r="N80" s="20"/>
-      <c r="O80" s="21">
+      <c r="O80" s="22">
         <v>0.0</v>
       </c>
       <c r="P80" s="20"/>
@@ -11483,7 +11489,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B81" s="20"/>
       <c r="C81" s="20"/>
@@ -11526,7 +11532,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B82" s="15">
         <v>12.61</v>
@@ -11565,7 +11571,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B83" s="20"/>
       <c r="C83" s="15">
@@ -11596,7 +11602,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B84" s="20"/>
       <c r="C84" s="15">
@@ -11649,7 +11655,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B85" s="20"/>
       <c r="C85" s="20"/>
@@ -11708,7 +11714,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B86" s="20"/>
       <c r="C86" s="15">
@@ -11757,7 +11763,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B87" s="20"/>
       <c r="C87" s="20"/>
@@ -11767,7 +11773,7 @@
       <c r="E87" s="20">
         <v>0.0</v>
       </c>
-      <c r="F87" s="21">
+      <c r="F87" s="22">
         <v>0.0</v>
       </c>
       <c r="G87" s="20"/>
@@ -11790,7 +11796,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B88" s="20"/>
       <c r="C88" s="15">
@@ -11821,7 +11827,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B89" s="20"/>
       <c r="C89" s="20"/>
@@ -11850,7 +11856,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B90" s="20"/>
       <c r="C90" s="20"/>
@@ -11887,7 +11893,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B91" s="20"/>
       <c r="C91" s="20"/>
@@ -11920,7 +11926,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B92" s="20"/>
       <c r="C92" s="20"/>
@@ -11949,7 +11955,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B93" s="20">
         <v>0.0</v>
@@ -11980,7 +11986,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B94" s="18">
         <v>18.79</v>
@@ -12051,7 +12057,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B95" s="15">
         <v>4.16</v>
@@ -12094,7 +12100,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B96" s="18">
         <v>4.16</v>
@@ -12120,32 +12126,32 @@
       <c r="I96" s="18">
         <v>14.69</v>
       </c>
-      <c r="J96" s="23"/>
-      <c r="K96" s="23"/>
-      <c r="L96" s="23"/>
-      <c r="M96" s="23"/>
-      <c r="N96" s="23"/>
-      <c r="O96" s="23"/>
-      <c r="P96" s="23"/>
-      <c r="Q96" s="23"/>
-      <c r="R96" s="23"/>
-      <c r="S96" s="23"/>
-      <c r="T96" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="U96" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="V96" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="W96" s="23">
+      <c r="J96" s="24"/>
+      <c r="K96" s="24"/>
+      <c r="L96" s="24"/>
+      <c r="M96" s="24"/>
+      <c r="N96" s="24"/>
+      <c r="O96" s="24"/>
+      <c r="P96" s="24"/>
+      <c r="Q96" s="24"/>
+      <c r="R96" s="24"/>
+      <c r="S96" s="24"/>
+      <c r="T96" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="U96" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="V96" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="W96" s="24">
         <v>0.0</v>
       </c>
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B97" s="20"/>
       <c r="C97" s="20"/>
@@ -12174,7 +12180,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B98" s="18">
         <v>22.94</v>
@@ -12245,7 +12251,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B99" s="15">
         <v>51.07</v>
@@ -12316,7 +12322,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B100" s="14">
         <v>265.77</v>
@@ -12385,7 +12391,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B101" s="15">
         <v>21.63</v>
@@ -12405,16 +12411,16 @@
       <c r="G101" s="19">
         <v>-5.01</v>
       </c>
-      <c r="H101" s="25">
+      <c r="H101" s="26">
         <v>-154.23</v>
       </c>
-      <c r="I101" s="25">
+      <c r="I101" s="26">
         <v>-147.78</v>
       </c>
-      <c r="J101" s="25">
+      <c r="J101" s="26">
         <v>-133.22</v>
       </c>
-      <c r="K101" s="25">
+      <c r="K101" s="26">
         <v>-109.81</v>
       </c>
       <c r="L101" s="19">
@@ -12454,7 +12460,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B102" s="20"/>
       <c r="C102" s="20"/>
@@ -12491,7 +12497,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B103" s="20"/>
       <c r="C103" s="20"/>
@@ -12520,7 +12526,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B104" s="17">
         <v>338.47</v>
@@ -12591,7 +12597,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B105" s="20"/>
       <c r="C105" s="20"/>
@@ -12640,13 +12646,13 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="B106" s="23"/>
-      <c r="C106" s="23"/>
-      <c r="D106" s="23"/>
-      <c r="E106" s="23"/>
-      <c r="F106" s="23"/>
+        <v>254</v>
+      </c>
+      <c r="B106" s="24"/>
+      <c r="C106" s="24"/>
+      <c r="D106" s="24"/>
+      <c r="E106" s="24"/>
+      <c r="F106" s="24"/>
       <c r="G106" s="18">
         <v>1.97</v>
       </c>
@@ -12674,18 +12680,18 @@
       <c r="O106" s="18">
         <v>1.18</v>
       </c>
-      <c r="P106" s="23"/>
-      <c r="Q106" s="23"/>
-      <c r="R106" s="23"/>
-      <c r="S106" s="23"/>
-      <c r="T106" s="23"/>
-      <c r="U106" s="23"/>
-      <c r="V106" s="23"/>
-      <c r="W106" s="23"/>
+      <c r="P106" s="24"/>
+      <c r="Q106" s="24"/>
+      <c r="R106" s="24"/>
+      <c r="S106" s="24"/>
+      <c r="T106" s="24"/>
+      <c r="U106" s="24"/>
+      <c r="V106" s="24"/>
+      <c r="W106" s="24"/>
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B107" s="20"/>
       <c r="C107" s="20"/>
@@ -12694,15 +12700,15 @@
       <c r="F107" s="20">
         <v>0.0</v>
       </c>
-      <c r="G107" s="21">
+      <c r="G107" s="22">
         <v>0.0</v>
       </c>
       <c r="H107" s="20"/>
       <c r="I107" s="20"/>
-      <c r="J107" s="21">
-        <v>0.0</v>
-      </c>
-      <c r="K107" s="21">
+      <c r="J107" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="K107" s="22">
         <v>0.0</v>
       </c>
       <c r="L107" s="20">
@@ -12722,7 +12728,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B108" s="17">
         <v>338.47</v>
@@ -12793,20 +12799,20 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B109" s="20"/>
-      <c r="C109" s="21">
+      <c r="C109" s="22">
         <v>0.0</v>
       </c>
       <c r="D109" s="20"/>
       <c r="E109" s="20"/>
       <c r="F109" s="20"/>
       <c r="G109" s="20"/>
-      <c r="H109" s="21">
-        <v>0.0</v>
-      </c>
-      <c r="I109" s="21">
+      <c r="H109" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="I109" s="22">
         <v>0.0</v>
       </c>
       <c r="J109" s="20"/>
@@ -12828,7 +12834,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B110" s="17">
         <v>361.41</v>
@@ -12899,7 +12905,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B111" s="15">
         <v>51.07</v>
@@ -12970,7 +12976,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B112" s="20">
         <v>0.0</v>
@@ -13041,7 +13047,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B113" s="15">
         <v>51.07</v>
@@ -13112,7 +13118,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B114" s="20"/>
       <c r="C114" s="15">
@@ -13153,7 +13159,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B115" s="20"/>
       <c r="C115" s="15">
@@ -13194,7 +13200,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B116" s="20"/>
       <c r="C116" s="15">
@@ -13235,7 +13241,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B117" s="20"/>
       <c r="C117" s="15">
@@ -13276,7 +13282,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B118" s="15">
         <v>51.07</v>
@@ -13347,7 +13353,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B119" s="15">
         <v>51.07</v>
@@ -13418,7 +13424,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B120" s="15">
         <v>1.0</v>
@@ -13489,7 +13495,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B121" s="20">
         <v>0.0</v>
@@ -14458,7 +14464,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -14844,75 +14850,75 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -15010,7 +15016,7 @@
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B19" s="15">
         <v>12.18</v>
@@ -15081,7 +15087,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B20" s="19">
         <v>-0.32</v>
@@ -15124,7 +15130,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B21" s="15">
         <v>9.15</v>
@@ -15173,7 +15179,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
@@ -15216,7 +15222,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="20"/>
@@ -15251,7 +15257,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
@@ -15262,7 +15268,7 @@
       <c r="H24" s="20"/>
       <c r="I24" s="20"/>
       <c r="J24" s="20"/>
-      <c r="K24" s="21">
+      <c r="K24" s="22">
         <v>0.0</v>
       </c>
       <c r="L24" s="20"/>
@@ -15280,7 +15286,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -15311,7 +15317,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -15340,7 +15346,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B27" s="15">
         <v>4.45</v>
@@ -15401,7 +15407,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B28" s="15">
         <v>0.27</v>
@@ -15438,7 +15444,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="20"/>
@@ -15487,7 +15493,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
@@ -15520,7 +15526,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -15553,7 +15559,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
@@ -15586,7 +15592,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B33" s="19">
         <v>-0.32</v>
@@ -15657,7 +15663,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B34" s="19">
         <v>-1.52</v>
@@ -15728,7 +15734,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B35" s="19">
         <v>-2.75</v>
@@ -15763,7 +15769,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="13" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B36" s="15">
         <v>4.67</v>
@@ -15834,7 +15840,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="20"/>
@@ -15865,7 +15871,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
@@ -15900,7 +15906,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="20"/>
@@ -15937,7 +15943,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B40" s="20"/>
       <c r="C40" s="20"/>
@@ -15962,7 +15968,7 @@
       <c r="R40" s="19">
         <v>-0.06</v>
       </c>
-      <c r="S40" s="21">
+      <c r="S40" s="22">
         <v>0.0</v>
       </c>
       <c r="T40" s="19">
@@ -15974,13 +15980,13 @@
       <c r="V40" s="19">
         <v>-0.06</v>
       </c>
-      <c r="W40" s="21">
+      <c r="W40" s="22">
         <v>0.0</v>
       </c>
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B41" s="20"/>
       <c r="C41" s="20"/>
@@ -16013,7 +16019,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
@@ -16046,9 +16052,9 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="B43" s="21">
+        <v>293</v>
+      </c>
+      <c r="B43" s="22">
         <v>0.0</v>
       </c>
       <c r="C43" s="20">
@@ -16056,13 +16062,13 @@
       </c>
       <c r="D43" s="20"/>
       <c r="E43" s="20"/>
-      <c r="F43" s="21">
+      <c r="F43" s="22">
         <v>0.0</v>
       </c>
       <c r="G43" s="20"/>
       <c r="H43" s="20"/>
       <c r="I43" s="20"/>
-      <c r="J43" s="21">
+      <c r="J43" s="22">
         <v>0.0</v>
       </c>
       <c r="K43" s="20"/>
@@ -16074,7 +16080,7 @@
       <c r="O43" s="20"/>
       <c r="P43" s="20"/>
       <c r="Q43" s="20"/>
-      <c r="R43" s="21">
+      <c r="R43" s="22">
         <v>0.0</v>
       </c>
       <c r="S43" s="20"/>
@@ -16085,7 +16091,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="16" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B44" s="18">
         <v>25.81</v>
@@ -16108,55 +16114,55 @@
       <c r="H44" s="18">
         <v>3.97</v>
       </c>
-      <c r="I44" s="22">
+      <c r="I44" s="23">
         <v>-15.19</v>
       </c>
-      <c r="J44" s="22">
+      <c r="J44" s="23">
         <v>-22.06</v>
       </c>
-      <c r="K44" s="22">
+      <c r="K44" s="23">
         <v>-19.28</v>
       </c>
-      <c r="L44" s="22">
+      <c r="L44" s="23">
         <v>-12.89</v>
       </c>
-      <c r="M44" s="22">
+      <c r="M44" s="23">
         <v>-21.2</v>
       </c>
-      <c r="N44" s="22">
+      <c r="N44" s="23">
         <v>-17.39</v>
       </c>
-      <c r="O44" s="22">
+      <c r="O44" s="23">
         <v>-24.58</v>
       </c>
-      <c r="P44" s="22">
+      <c r="P44" s="23">
         <v>-10.81</v>
       </c>
-      <c r="Q44" s="22">
+      <c r="Q44" s="23">
         <v>-24.96</v>
       </c>
-      <c r="R44" s="22">
+      <c r="R44" s="23">
         <v>-89.0</v>
       </c>
-      <c r="S44" s="22">
+      <c r="S44" s="23">
         <v>-65.66</v>
       </c>
-      <c r="T44" s="22">
+      <c r="T44" s="23">
         <v>-24.73</v>
       </c>
-      <c r="U44" s="22">
+      <c r="U44" s="23">
         <v>-34.49</v>
       </c>
-      <c r="V44" s="22">
+      <c r="V44" s="23">
         <v>-8.47</v>
       </c>
-      <c r="W44" s="22">
+      <c r="W44" s="23">
         <v>-3.08</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B45" s="19">
         <v>-0.26</v>
@@ -16272,7 +16278,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B47" s="19">
         <v>-3.39</v>
@@ -16325,7 +16331,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
@@ -16356,7 +16362,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B49" s="19">
         <v>-0.29</v>
@@ -16411,7 +16417,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="20"/>
@@ -16444,7 +16450,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B51" s="19">
         <v>-1.22</v>
@@ -16481,7 +16487,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B52" s="20"/>
       <c r="C52" s="20"/>
@@ -16512,7 +16518,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B53" s="20"/>
       <c r="C53" s="20"/>
@@ -16545,7 +16551,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="15">
@@ -16574,7 +16580,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B55" s="20"/>
       <c r="C55" s="20"/>
@@ -16611,7 +16617,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
@@ -16636,7 +16642,7 @@
       <c r="T56" s="19">
         <v>-0.1</v>
       </c>
-      <c r="U56" s="21">
+      <c r="U56" s="22">
         <v>0.0</v>
       </c>
       <c r="V56" s="15">
@@ -16648,7 +16654,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B57" s="20"/>
       <c r="C57" s="20"/>
@@ -16681,7 +16687,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B58" s="20"/>
       <c r="C58" s="20"/>
@@ -16691,7 +16697,7 @@
       <c r="G58" s="20"/>
       <c r="H58" s="20"/>
       <c r="I58" s="20"/>
-      <c r="J58" s="21">
+      <c r="J58" s="22">
         <v>0.0</v>
       </c>
       <c r="K58" s="20"/>
@@ -16710,54 +16716,54 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="B59" s="22">
+        <v>307</v>
+      </c>
+      <c r="B59" s="23">
         <v>-5.14</v>
       </c>
-      <c r="C59" s="22">
+      <c r="C59" s="23">
         <v>-9.86</v>
       </c>
-      <c r="D59" s="22">
+      <c r="D59" s="23">
         <v>-21.01</v>
       </c>
-      <c r="E59" s="22">
+      <c r="E59" s="23">
         <v>-33.19</v>
       </c>
-      <c r="F59" s="22">
+      <c r="F59" s="23">
         <v>-11.56</v>
       </c>
       <c r="G59" s="18">
         <v>64.85</v>
       </c>
-      <c r="H59" s="22">
+      <c r="H59" s="23">
         <v>-1.1</v>
       </c>
-      <c r="I59" s="22">
+      <c r="I59" s="23">
         <v>-2.7</v>
       </c>
-      <c r="J59" s="22">
+      <c r="J59" s="23">
         <v>-5.02</v>
       </c>
-      <c r="K59" s="22">
+      <c r="K59" s="23">
         <v>-1.35</v>
       </c>
-      <c r="L59" s="22">
+      <c r="L59" s="23">
         <v>-1.49</v>
       </c>
-      <c r="M59" s="22">
+      <c r="M59" s="23">
         <v>-1.88</v>
       </c>
-      <c r="N59" s="22">
+      <c r="N59" s="23">
         <v>-1.56</v>
       </c>
-      <c r="O59" s="22">
+      <c r="O59" s="23">
         <v>-2.08</v>
       </c>
-      <c r="P59" s="22">
+      <c r="P59" s="23">
         <v>-4.57</v>
       </c>
-      <c r="Q59" s="22">
+      <c r="Q59" s="23">
         <v>-1.37</v>
       </c>
       <c r="R59" s="18">
@@ -16766,22 +16772,22 @@
       <c r="S59" s="18">
         <v>36.49</v>
       </c>
-      <c r="T59" s="22">
+      <c r="T59" s="23">
         <v>-1.89</v>
       </c>
-      <c r="U59" s="22">
+      <c r="U59" s="23">
         <v>-2.37</v>
       </c>
-      <c r="V59" s="22">
+      <c r="V59" s="23">
         <v>-1.48</v>
       </c>
-      <c r="W59" s="22">
+      <c r="W59" s="23">
         <v>-1.78</v>
       </c>
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B60" s="20"/>
       <c r="C60" s="20"/>
@@ -16822,7 +16828,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
@@ -16851,7 +16857,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B62" s="19">
         <v>-3.47</v>
@@ -16890,7 +16896,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
@@ -16943,7 +16949,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
@@ -16996,7 +17002,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="13" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B65" s="19">
         <v>-0.27</v>
@@ -17035,7 +17041,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
@@ -17064,7 +17070,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="13" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="15">
@@ -17109,7 +17115,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
@@ -17140,7 +17146,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="13" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B69" s="19">
         <v>-0.11</v>
@@ -17171,13 +17177,13 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
       <c r="D70" s="20"/>
       <c r="E70" s="20"/>
-      <c r="F70" s="21">
+      <c r="F70" s="22">
         <v>0.0</v>
       </c>
       <c r="G70" s="20"/>
@@ -17200,36 +17206,36 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="16" t="s">
-        <v>318</v>
-      </c>
-      <c r="B71" s="22">
+        <v>319</v>
+      </c>
+      <c r="B71" s="23">
         <v>-3.84</v>
       </c>
-      <c r="C71" s="22">
+      <c r="C71" s="23">
         <v>-1.73</v>
       </c>
-      <c r="D71" s="22">
+      <c r="D71" s="23">
         <v>-1.32</v>
       </c>
-      <c r="E71" s="22">
+      <c r="E71" s="23">
         <v>-1.92</v>
       </c>
-      <c r="F71" s="22">
+      <c r="F71" s="23">
         <v>-3.16</v>
       </c>
-      <c r="G71" s="22">
+      <c r="G71" s="23">
         <v>-3.07</v>
       </c>
-      <c r="H71" s="22">
+      <c r="H71" s="23">
         <v>-3.24</v>
       </c>
       <c r="I71" s="18">
         <v>18.97</v>
       </c>
-      <c r="J71" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="K71" s="22">
+      <c r="J71" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="K71" s="23">
         <v>-0.05</v>
       </c>
       <c r="L71" s="18">
@@ -17241,7 +17247,7 @@
       <c r="N71" s="18">
         <v>43.22</v>
       </c>
-      <c r="O71" s="22">
+      <c r="O71" s="23">
         <v>-0.03</v>
       </c>
       <c r="P71" s="18">
@@ -17250,10 +17256,10 @@
       <c r="Q71" s="18">
         <v>20.05</v>
       </c>
-      <c r="R71" s="22">
+      <c r="R71" s="23">
         <v>-0.05</v>
       </c>
-      <c r="S71" s="22">
+      <c r="S71" s="23">
         <v>-0.04</v>
       </c>
       <c r="T71" s="17">
@@ -17271,7 +17277,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B72" s="20"/>
       <c r="C72" s="20"/>
@@ -17302,7 +17308,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B73" s="14">
         <v>170.95</v>
@@ -17373,7 +17379,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B74" s="14">
         <v>187.78</v>
@@ -17444,7 +17450,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="13" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
@@ -17475,12 +17481,12 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="16" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B76" s="18">
         <v>16.83</v>
       </c>
-      <c r="C76" s="22">
+      <c r="C76" s="23">
         <v>-9.94</v>
       </c>
       <c r="D76" s="18">
@@ -17495,19 +17501,19 @@
       <c r="G76" s="17">
         <v>108.52</v>
       </c>
-      <c r="H76" s="22">
+      <c r="H76" s="23">
         <v>-0.37</v>
       </c>
       <c r="I76" s="18">
         <v>1.07</v>
       </c>
-      <c r="J76" s="22">
+      <c r="J76" s="23">
         <v>-27.08</v>
       </c>
-      <c r="K76" s="22">
+      <c r="K76" s="23">
         <v>-20.67</v>
       </c>
-      <c r="L76" s="22">
+      <c r="L76" s="23">
         <v>-9.94</v>
       </c>
       <c r="M76" s="18">
@@ -17516,31 +17522,31 @@
       <c r="N76" s="18">
         <v>24.28</v>
       </c>
-      <c r="O76" s="22">
+      <c r="O76" s="23">
         <v>-26.69</v>
       </c>
-      <c r="P76" s="22">
+      <c r="P76" s="23">
         <v>-7.29</v>
       </c>
-      <c r="Q76" s="22">
+      <c r="Q76" s="23">
         <v>-6.29</v>
       </c>
-      <c r="R76" s="22">
+      <c r="R76" s="23">
         <v>-74.94</v>
       </c>
-      <c r="S76" s="22">
+      <c r="S76" s="23">
         <v>-28.53</v>
       </c>
       <c r="T76" s="18">
         <v>89.23</v>
       </c>
-      <c r="U76" s="22">
+      <c r="U76" s="23">
         <v>-32.81</v>
       </c>
       <c r="V76" s="18">
         <v>74.74</v>
       </c>
-      <c r="W76" s="22">
+      <c r="W76" s="23">
         <v>-4.82</v>
       </c>
     </row>
@@ -18490,7 +18496,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -18657,13 +18663,13 @@
         <v>39</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -18976,7 +18982,7 @@
     </row>
     <row r="17">
       <c r="A17" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -19071,2127 +19077,2127 @@
         <v>69</v>
       </c>
       <c r="W18" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="X18" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Y18" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="26" t="s">
-        <v>332</v>
-      </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="27"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="27"/>
-      <c r="O19" s="27"/>
-      <c r="P19" s="27"/>
-      <c r="Q19" s="27"/>
-      <c r="R19" s="27"/>
-      <c r="S19" s="27"/>
-      <c r="T19" s="27"/>
-      <c r="U19" s="27"/>
-      <c r="V19" s="27"/>
-      <c r="W19" s="27"/>
-      <c r="X19" s="27"/>
-      <c r="Y19" s="27"/>
+      <c r="A19" s="27" t="s">
+        <v>333</v>
+      </c>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="28"/>
+      <c r="V19" s="28"/>
+      <c r="W19" s="28"/>
+      <c r="X19" s="28"/>
+      <c r="Y19" s="28"/>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="28" t="s">
-        <v>332</v>
-      </c>
-      <c r="B20" s="29">
+      <c r="A20" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="B20" s="30">
         <v>518.44</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <v>1968.29</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <v>3393.36</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <v>4552.06</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <v>2947.84</v>
       </c>
-      <c r="G20" s="29">
+      <c r="G20" s="30">
         <v>215.65</v>
       </c>
-      <c r="H20" s="29">
+      <c r="H20" s="30">
         <v>157.23</v>
       </c>
-      <c r="I20" s="29">
+      <c r="I20" s="30">
         <v>264.55</v>
       </c>
-      <c r="J20" s="29">
+      <c r="J20" s="30">
         <v>439.48</v>
       </c>
-      <c r="K20" s="29">
+      <c r="K20" s="30">
         <v>489.03</v>
       </c>
-      <c r="L20" s="29">
+      <c r="L20" s="30">
         <v>684.02</v>
       </c>
-      <c r="M20" s="29">
+      <c r="M20" s="30">
         <v>368.99</v>
       </c>
-      <c r="N20" s="29">
+      <c r="N20" s="30">
         <v>162.26</v>
       </c>
-      <c r="O20" s="29">
+      <c r="O20" s="30">
         <v>114.07</v>
       </c>
-      <c r="P20" s="29">
+      <c r="P20" s="30">
         <v>148.25</v>
       </c>
-      <c r="Q20" s="30">
+      <c r="Q20" s="31">
         <v>70.91</v>
       </c>
-      <c r="R20" s="29">
+      <c r="R20" s="30">
         <v>129.7</v>
       </c>
-      <c r="S20" s="29">
+      <c r="S20" s="30">
         <v>569.26</v>
       </c>
-      <c r="T20" s="29">
+      <c r="T20" s="30">
         <v>860.06</v>
       </c>
-      <c r="U20" s="29">
+      <c r="U20" s="30">
         <v>367.13</v>
       </c>
-      <c r="V20" s="31"/>
-      <c r="W20" s="31"/>
-      <c r="X20" s="31"/>
-      <c r="Y20" s="31"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="32"/>
+      <c r="Y20" s="32"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="28" t="s">
-        <v>333</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="A21" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="B21" s="30">
         <v>2676.0</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>2615.44</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>2253.23</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>1627.47</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>804.95</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <v>313.19</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="30">
         <v>406.86</v>
       </c>
-      <c r="I21" s="29">
+      <c r="I21" s="30">
         <v>449.22</v>
       </c>
-      <c r="J21" s="29">
+      <c r="J21" s="30">
         <v>428.76</v>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="30">
         <v>363.68</v>
       </c>
-      <c r="L21" s="29">
+      <c r="L21" s="30">
         <v>295.52</v>
       </c>
-      <c r="M21" s="29">
+      <c r="M21" s="30">
         <v>172.9</v>
       </c>
-      <c r="N21" s="29">
+      <c r="N21" s="30">
         <v>125.04</v>
       </c>
-      <c r="O21" s="29">
+      <c r="O21" s="30">
         <v>206.44</v>
       </c>
-      <c r="P21" s="29">
+      <c r="P21" s="30">
         <v>355.63</v>
       </c>
-      <c r="Q21" s="29">
+      <c r="Q21" s="30">
         <v>399.41</v>
       </c>
-      <c r="R21" s="31"/>
-      <c r="S21" s="31"/>
-      <c r="T21" s="31"/>
-      <c r="U21" s="31"/>
-      <c r="V21" s="31"/>
-      <c r="W21" s="31"/>
-      <c r="X21" s="31"/>
-      <c r="Y21" s="31"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="32"/>
+      <c r="X21" s="32"/>
+      <c r="Y21" s="32"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="27"/>
-      <c r="M22" s="27"/>
-      <c r="N22" s="27"/>
-      <c r="O22" s="27"/>
-      <c r="P22" s="27"/>
-      <c r="Q22" s="27"/>
-      <c r="R22" s="27"/>
-      <c r="S22" s="27"/>
-      <c r="T22" s="27"/>
-      <c r="U22" s="27"/>
-      <c r="V22" s="27"/>
-      <c r="W22" s="27"/>
-      <c r="X22" s="27"/>
-      <c r="Y22" s="27"/>
+      <c r="A22" s="27" t="s">
+        <v>335</v>
+      </c>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
+      <c r="T22" s="28"/>
+      <c r="U22" s="28"/>
+      <c r="V22" s="28"/>
+      <c r="W22" s="28"/>
+      <c r="X22" s="28"/>
+      <c r="Y22" s="28"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="28" t="s">
-        <v>334</v>
-      </c>
-      <c r="B23" s="29">
+      <c r="A23" s="29" t="s">
+        <v>335</v>
+      </c>
+      <c r="B23" s="30">
         <v>681.29</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="30">
         <v>2136.6</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="30">
         <v>3623.44</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="30">
         <v>4734.91</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="30">
         <v>3074.09</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="30">
         <v>229.59</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="30">
         <v>170.14</v>
       </c>
-      <c r="I23" s="29">
+      <c r="I23" s="30">
         <v>294.43</v>
       </c>
-      <c r="J23" s="29">
+      <c r="J23" s="30">
         <v>496.57</v>
       </c>
-      <c r="K23" s="29">
+      <c r="K23" s="30">
         <v>566.89</v>
       </c>
-      <c r="L23" s="29">
+      <c r="L23" s="30">
         <v>771.87</v>
       </c>
-      <c r="M23" s="29">
+      <c r="M23" s="30">
         <v>401.81</v>
       </c>
-      <c r="N23" s="29">
+      <c r="N23" s="30">
         <v>170.46</v>
       </c>
-      <c r="O23" s="29">
+      <c r="O23" s="30">
         <v>148.47</v>
       </c>
-      <c r="P23" s="29">
+      <c r="P23" s="30">
         <v>189.76</v>
       </c>
-      <c r="Q23" s="29">
+      <c r="Q23" s="30">
         <v>120.55</v>
       </c>
-      <c r="R23" s="29">
+      <c r="R23" s="30">
         <v>254.29</v>
       </c>
-      <c r="S23" s="29">
+      <c r="S23" s="30">
         <v>720.96</v>
       </c>
-      <c r="T23" s="29">
+      <c r="T23" s="30">
         <v>924.03</v>
       </c>
-      <c r="U23" s="29">
+      <c r="U23" s="30">
         <v>462.01</v>
       </c>
-      <c r="V23" s="31"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="31"/>
+      <c r="V23" s="32"/>
+      <c r="W23" s="32"/>
+      <c r="X23" s="32"/>
+      <c r="Y23" s="32"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="28" t="s">
-        <v>335</v>
-      </c>
-      <c r="B24" s="29">
+      <c r="A24" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="B24" s="30">
         <v>2850.07</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="30">
         <v>2759.72</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <v>2366.43</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="30">
         <v>1700.63</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <v>852.96</v>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="30">
         <v>351.52</v>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="30">
         <v>459.98</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I24" s="30">
         <v>506.31</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="30">
         <v>481.52</v>
       </c>
-      <c r="K24" s="29">
+      <c r="K24" s="30">
         <v>411.9</v>
       </c>
-      <c r="L24" s="29">
+      <c r="L24" s="30">
         <v>336.48</v>
       </c>
-      <c r="M24" s="29">
+      <c r="M24" s="30">
         <v>206.21</v>
       </c>
-      <c r="N24" s="29">
+      <c r="N24" s="30">
         <v>176.71</v>
       </c>
-      <c r="O24" s="29">
+      <c r="O24" s="30">
         <v>286.81</v>
       </c>
-      <c r="P24" s="29">
+      <c r="P24" s="30">
         <v>441.92</v>
       </c>
-      <c r="Q24" s="29">
+      <c r="Q24" s="30">
         <v>496.37</v>
       </c>
-      <c r="R24" s="31"/>
-      <c r="S24" s="31"/>
-      <c r="T24" s="31"/>
-      <c r="U24" s="31"/>
-      <c r="V24" s="31"/>
-      <c r="W24" s="31"/>
-      <c r="X24" s="31"/>
-      <c r="Y24" s="31"/>
+      <c r="R24" s="32"/>
+      <c r="S24" s="32"/>
+      <c r="T24" s="32"/>
+      <c r="U24" s="32"/>
+      <c r="V24" s="32"/>
+      <c r="W24" s="32"/>
+      <c r="X24" s="32"/>
+      <c r="Y24" s="32"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="26" t="s">
-        <v>336</v>
-      </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="27"/>
-      <c r="U25" s="27"/>
-      <c r="V25" s="27"/>
-      <c r="W25" s="27"/>
-      <c r="X25" s="27"/>
-      <c r="Y25" s="27"/>
+      <c r="A25" s="27" t="s">
+        <v>337</v>
+      </c>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="28"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
+      <c r="T25" s="28"/>
+      <c r="U25" s="28"/>
+      <c r="V25" s="28"/>
+      <c r="W25" s="28"/>
+      <c r="X25" s="28"/>
+      <c r="Y25" s="28"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="28" t="s">
-        <v>337</v>
-      </c>
-      <c r="B26" s="30">
+      <c r="A26" s="29" t="s">
+        <v>338</v>
+      </c>
+      <c r="B26" s="31">
         <v>13.34</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="31">
         <v>42.0</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="31">
         <v>71.65</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="31">
         <v>94.0</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="31">
         <v>63.6</v>
       </c>
-      <c r="G26" s="30">
+      <c r="G26" s="31">
         <v>4.75</v>
       </c>
-      <c r="H26" s="30">
+      <c r="H26" s="31">
         <v>3.52</v>
       </c>
-      <c r="I26" s="30">
+      <c r="I26" s="31">
         <v>6.7</v>
       </c>
-      <c r="J26" s="30">
+      <c r="J26" s="31">
         <v>11.3</v>
       </c>
-      <c r="K26" s="30">
+      <c r="K26" s="31">
         <v>12.9</v>
       </c>
-      <c r="L26" s="30">
+      <c r="L26" s="31">
         <v>17.7</v>
       </c>
-      <c r="M26" s="30">
+      <c r="M26" s="31">
         <v>10.2</v>
       </c>
-      <c r="N26" s="30">
+      <c r="N26" s="31">
         <v>5.87</v>
       </c>
-      <c r="O26" s="30">
+      <c r="O26" s="31">
         <v>5.11</v>
       </c>
-      <c r="P26" s="30">
+      <c r="P26" s="31">
         <v>7.51</v>
       </c>
-      <c r="Q26" s="30">
+      <c r="Q26" s="31">
         <v>5.0</v>
       </c>
-      <c r="R26" s="30">
+      <c r="R26" s="31">
         <v>10.54</v>
       </c>
-      <c r="S26" s="30">
+      <c r="S26" s="31">
         <v>29.89</v>
       </c>
-      <c r="T26" s="30">
+      <c r="T26" s="31">
         <v>42.14</v>
       </c>
-      <c r="U26" s="30">
+      <c r="U26" s="31">
         <v>21.07</v>
       </c>
-      <c r="V26" s="31"/>
-      <c r="W26" s="31"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="31"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="32"/>
+      <c r="X26" s="32"/>
+      <c r="Y26" s="32"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="28" t="s">
-        <v>338</v>
-      </c>
-      <c r="B27" s="30">
+      <c r="A27" s="29" t="s">
+        <v>339</v>
+      </c>
+      <c r="B27" s="31">
         <v>56.92</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>55.2</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>47.5</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="31">
         <v>34.51</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="31">
         <v>17.97</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="31">
         <v>7.83</v>
       </c>
-      <c r="H27" s="30">
+      <c r="H27" s="31">
         <v>10.42</v>
       </c>
-      <c r="I27" s="30">
+      <c r="I27" s="31">
         <v>11.76</v>
       </c>
-      <c r="J27" s="30">
+      <c r="J27" s="31">
         <v>11.59</v>
       </c>
-      <c r="K27" s="30">
+      <c r="K27" s="31">
         <v>10.36</v>
       </c>
-      <c r="L27" s="30">
+      <c r="L27" s="31">
         <v>9.28</v>
       </c>
-      <c r="M27" s="30">
+      <c r="M27" s="31">
         <v>6.74</v>
       </c>
-      <c r="N27" s="30">
+      <c r="N27" s="31">
         <v>6.81</v>
       </c>
-      <c r="O27" s="30">
+      <c r="O27" s="31">
         <v>11.61</v>
       </c>
-      <c r="P27" s="30">
+      <c r="P27" s="31">
         <v>19.02</v>
       </c>
-      <c r="Q27" s="30">
+      <c r="Q27" s="31">
         <v>21.73</v>
       </c>
-      <c r="R27" s="31"/>
-      <c r="S27" s="31"/>
-      <c r="T27" s="31"/>
-      <c r="U27" s="31"/>
-      <c r="V27" s="31"/>
-      <c r="W27" s="31"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="31"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="32"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="32"/>
+      <c r="X27" s="32"/>
+      <c r="Y27" s="32"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="26" t="s">
-        <v>339</v>
-      </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
-      <c r="M28" s="27"/>
-      <c r="N28" s="27"/>
-      <c r="O28" s="27"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
-      <c r="T28" s="27"/>
-      <c r="U28" s="27"/>
-      <c r="V28" s="27"/>
-      <c r="W28" s="27"/>
-      <c r="X28" s="27"/>
-      <c r="Y28" s="27"/>
+      <c r="A28" s="27" t="s">
+        <v>340</v>
+      </c>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="28"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
+      <c r="U28" s="28"/>
+      <c r="V28" s="28"/>
+      <c r="W28" s="28"/>
+      <c r="X28" s="28"/>
+      <c r="Y28" s="28"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="28" t="s">
-        <v>340</v>
-      </c>
-      <c r="B29" s="32">
+      <c r="A29" s="29" t="s">
+        <v>341</v>
+      </c>
+      <c r="B29" s="33">
         <v>-1.21</v>
       </c>
-      <c r="C29" s="33">
+      <c r="C29" s="34">
         <v>0.22</v>
       </c>
-      <c r="D29" s="33">
+      <c r="D29" s="34">
         <v>1.26</v>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="34">
         <v>1.33</v>
       </c>
-      <c r="F29" s="33">
+      <c r="F29" s="34">
         <v>1.43</v>
       </c>
-      <c r="G29" s="33">
+      <c r="G29" s="34">
         <v>0.9</v>
       </c>
-      <c r="H29" s="32">
+      <c r="H29" s="33">
         <v>-11.27</v>
       </c>
-      <c r="I29" s="32">
+      <c r="I29" s="33">
         <v>-9.21</v>
       </c>
-      <c r="J29" s="32">
+      <c r="J29" s="33">
         <v>-4.15</v>
       </c>
-      <c r="K29" s="32">
+      <c r="K29" s="33">
         <v>-2.55</v>
       </c>
-      <c r="L29" s="32">
+      <c r="L29" s="33">
         <v>-3.08</v>
       </c>
-      <c r="M29" s="32">
+      <c r="M29" s="33">
         <v>-4.89</v>
       </c>
-      <c r="N29" s="32">
+      <c r="N29" s="33">
         <v>-15.68</v>
       </c>
-      <c r="O29" s="32">
+      <c r="O29" s="33">
         <v>-11.09</v>
       </c>
-      <c r="P29" s="32">
+      <c r="P29" s="33">
         <v>-14.82</v>
       </c>
-      <c r="Q29" s="32">
+      <c r="Q29" s="33">
         <v>-75.13</v>
       </c>
-      <c r="R29" s="32">
+      <c r="R29" s="33">
         <v>-26.86</v>
       </c>
-      <c r="S29" s="32">
+      <c r="S29" s="33">
         <v>-3.79</v>
       </c>
-      <c r="T29" s="32">
+      <c r="T29" s="33">
         <v>-4.27</v>
       </c>
-      <c r="U29" s="32">
+      <c r="U29" s="33">
         <v>-2.78</v>
       </c>
-      <c r="V29" s="33"/>
-      <c r="W29" s="33"/>
-      <c r="X29" s="33"/>
-      <c r="Y29" s="33"/>
+      <c r="V29" s="34"/>
+      <c r="W29" s="34"/>
+      <c r="X29" s="34"/>
+      <c r="Y29" s="34"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="28" t="s">
-        <v>341</v>
-      </c>
-      <c r="B30" s="33">
+      <c r="A30" s="29" t="s">
+        <v>342</v>
+      </c>
+      <c r="B30" s="34">
         <v>1.05</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C30" s="34">
         <v>1.16</v>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="34">
         <v>1.14</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="34">
         <v>0.69</v>
       </c>
-      <c r="F30" s="32">
+      <c r="F30" s="33">
         <v>-0.59</v>
       </c>
-      <c r="G30" s="32">
+      <c r="G30" s="33">
         <v>-4.52</v>
       </c>
-      <c r="H30" s="32">
+      <c r="H30" s="33">
         <v>-4.52</v>
       </c>
-      <c r="I30" s="32">
+      <c r="I30" s="33">
         <v>-4.18</v>
       </c>
-      <c r="J30" s="32">
+      <c r="J30" s="33">
         <v>-4.77</v>
       </c>
-      <c r="K30" s="32">
+      <c r="K30" s="33">
         <v>-5.52</v>
       </c>
-      <c r="L30" s="32">
+      <c r="L30" s="33">
         <v>-7.85</v>
       </c>
-      <c r="M30" s="32">
+      <c r="M30" s="33">
         <v>-20.34</v>
       </c>
-      <c r="N30" s="32">
+      <c r="N30" s="33">
         <v>-26.99</v>
       </c>
-      <c r="O30" s="32">
+      <c r="O30" s="33">
         <v>-16.19</v>
       </c>
-      <c r="P30" s="32">
+      <c r="P30" s="33">
         <v>-11.18</v>
       </c>
-      <c r="Q30" s="32">
+      <c r="Q30" s="33">
         <v>-9.3</v>
       </c>
-      <c r="R30" s="33"/>
-      <c r="S30" s="33"/>
-      <c r="T30" s="33"/>
-      <c r="U30" s="33"/>
-      <c r="V30" s="33"/>
-      <c r="W30" s="33"/>
-      <c r="X30" s="33"/>
-      <c r="Y30" s="33"/>
+      <c r="R30" s="34"/>
+      <c r="S30" s="34"/>
+      <c r="T30" s="34"/>
+      <c r="U30" s="34"/>
+      <c r="V30" s="34"/>
+      <c r="W30" s="34"/>
+      <c r="X30" s="34"/>
+      <c r="Y30" s="34"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="26" t="s">
-        <v>342</v>
-      </c>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27"/>
-      <c r="K31" s="27"/>
-      <c r="L31" s="27"/>
-      <c r="M31" s="27"/>
-      <c r="N31" s="27"/>
-      <c r="O31" s="27"/>
-      <c r="P31" s="27"/>
-      <c r="Q31" s="27"/>
-      <c r="R31" s="27"/>
-      <c r="S31" s="27"/>
-      <c r="T31" s="27"/>
-      <c r="U31" s="27"/>
-      <c r="V31" s="27"/>
-      <c r="W31" s="27"/>
-      <c r="X31" s="27"/>
-      <c r="Y31" s="27"/>
+      <c r="A31" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+      <c r="M31" s="28"/>
+      <c r="N31" s="28"/>
+      <c r="O31" s="28"/>
+      <c r="P31" s="28"/>
+      <c r="Q31" s="28"/>
+      <c r="R31" s="28"/>
+      <c r="S31" s="28"/>
+      <c r="T31" s="28"/>
+      <c r="U31" s="28"/>
+      <c r="V31" s="28"/>
+      <c r="W31" s="28"/>
+      <c r="X31" s="28"/>
+      <c r="Y31" s="28"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="28" t="s">
-        <v>343</v>
-      </c>
-      <c r="B32" s="30">
+      <c r="A32" s="29" t="s">
+        <v>344</v>
+      </c>
+      <c r="B32" s="31">
         <v>2.1</v>
       </c>
-      <c r="C32" s="30">
+      <c r="C32" s="31">
         <v>6.91</v>
       </c>
-      <c r="D32" s="30">
+      <c r="D32" s="31">
         <v>12.73</v>
       </c>
-      <c r="E32" s="30">
+      <c r="E32" s="31">
         <v>19.34</v>
       </c>
-      <c r="F32" s="30">
+      <c r="F32" s="31">
         <v>15.82</v>
       </c>
-      <c r="G32" s="30">
+      <c r="G32" s="31">
         <v>5.09</v>
       </c>
-      <c r="H32" s="30">
+      <c r="H32" s="31">
         <v>3.3</v>
       </c>
-      <c r="I32" s="30">
+      <c r="I32" s="31">
         <v>6.68</v>
       </c>
-      <c r="J32" s="30">
+      <c r="J32" s="31">
         <v>7.36</v>
       </c>
-      <c r="K32" s="30">
+      <c r="K32" s="31">
         <v>6.57</v>
       </c>
-      <c r="L32" s="30">
+      <c r="L32" s="31">
         <v>7.84</v>
       </c>
-      <c r="M32" s="30">
+      <c r="M32" s="31">
         <v>9.64</v>
       </c>
-      <c r="N32" s="30">
+      <c r="N32" s="31">
         <v>8.09</v>
       </c>
-      <c r="O32" s="30">
+      <c r="O32" s="31">
         <v>3.36</v>
       </c>
-      <c r="P32" s="30">
+      <c r="P32" s="31">
         <v>5.23</v>
       </c>
-      <c r="Q32" s="30">
+      <c r="Q32" s="31">
         <v>1.96</v>
       </c>
-      <c r="R32" s="30">
+      <c r="R32" s="31">
         <v>1.59</v>
       </c>
-      <c r="S32" s="30">
+      <c r="S32" s="31">
         <v>3.52</v>
       </c>
-      <c r="T32" s="30">
+      <c r="T32" s="31">
         <v>8.43</v>
       </c>
-      <c r="U32" s="30">
+      <c r="U32" s="31">
         <v>3.53</v>
       </c>
-      <c r="V32" s="31"/>
-      <c r="W32" s="31"/>
-      <c r="X32" s="31"/>
-      <c r="Y32" s="31"/>
+      <c r="V32" s="32"/>
+      <c r="W32" s="32"/>
+      <c r="X32" s="32"/>
+      <c r="Y32" s="32"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="28" t="s">
-        <v>344</v>
-      </c>
-      <c r="B33" s="30">
+      <c r="A33" s="29" t="s">
+        <v>345</v>
+      </c>
+      <c r="B33" s="31">
         <v>10.56</v>
       </c>
-      <c r="C33" s="30">
+      <c r="C33" s="31">
         <v>12.82</v>
       </c>
-      <c r="D33" s="30">
+      <c r="D33" s="31">
         <v>14.38</v>
       </c>
-      <c r="E33" s="30">
+      <c r="E33" s="31">
         <v>14.52</v>
       </c>
-      <c r="F33" s="30">
+      <c r="F33" s="31">
         <v>10.5</v>
       </c>
-      <c r="G33" s="30">
+      <c r="G33" s="31">
         <v>6.02</v>
       </c>
-      <c r="H33" s="30">
+      <c r="H33" s="31">
         <v>6.66</v>
       </c>
-      <c r="I33" s="30">
+      <c r="I33" s="31">
         <v>7.52</v>
       </c>
-      <c r="J33" s="30">
+      <c r="J33" s="31">
         <v>7.69</v>
       </c>
-      <c r="K33" s="30">
+      <c r="K33" s="31">
         <v>6.88</v>
       </c>
-      <c r="L33" s="30">
+      <c r="L33" s="31">
         <v>6.63</v>
       </c>
-      <c r="M33" s="30">
+      <c r="M33" s="31">
         <v>4.62</v>
       </c>
-      <c r="N33" s="30">
+      <c r="N33" s="31">
         <v>2.65</v>
       </c>
-      <c r="O33" s="30">
+      <c r="O33" s="31">
         <v>2.82</v>
       </c>
-      <c r="P33" s="30">
+      <c r="P33" s="31">
         <v>3.95</v>
       </c>
-      <c r="Q33" s="30">
+      <c r="Q33" s="31">
         <v>3.79</v>
       </c>
-      <c r="R33" s="31"/>
-      <c r="S33" s="31"/>
-      <c r="T33" s="31"/>
-      <c r="U33" s="31"/>
-      <c r="V33" s="31"/>
-      <c r="W33" s="31"/>
-      <c r="X33" s="31"/>
-      <c r="Y33" s="31"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="T33" s="32"/>
+      <c r="U33" s="32"/>
+      <c r="V33" s="32"/>
+      <c r="W33" s="32"/>
+      <c r="X33" s="32"/>
+      <c r="Y33" s="32"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="26" t="s">
-        <v>345</v>
-      </c>
-      <c r="B34" s="27"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="27"/>
-      <c r="K34" s="27"/>
-      <c r="L34" s="27"/>
-      <c r="M34" s="27"/>
-      <c r="N34" s="27"/>
-      <c r="O34" s="27"/>
-      <c r="P34" s="27"/>
-      <c r="Q34" s="27"/>
-      <c r="R34" s="27"/>
-      <c r="S34" s="27"/>
-      <c r="T34" s="27"/>
-      <c r="U34" s="27"/>
-      <c r="V34" s="27"/>
-      <c r="W34" s="27"/>
-      <c r="X34" s="27"/>
-      <c r="Y34" s="27"/>
+      <c r="A34" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28"/>
+      <c r="N34" s="28"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="28"/>
+      <c r="S34" s="28"/>
+      <c r="T34" s="28"/>
+      <c r="U34" s="28"/>
+      <c r="V34" s="28"/>
+      <c r="W34" s="28"/>
+      <c r="X34" s="28"/>
+      <c r="Y34" s="28"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="28" t="s">
-        <v>346</v>
-      </c>
-      <c r="B35" s="30">
+      <c r="A35" s="29" t="s">
+        <v>347</v>
+      </c>
+      <c r="B35" s="31">
         <v>2.34</v>
       </c>
-      <c r="C35" s="30">
+      <c r="C35" s="31">
         <v>7.54</v>
       </c>
-      <c r="D35" s="30">
+      <c r="D35" s="31">
         <v>13.15</v>
       </c>
-      <c r="E35" s="30">
+      <c r="E35" s="31">
         <v>19.48</v>
       </c>
-      <c r="F35" s="30">
+      <c r="F35" s="31">
         <v>15.85</v>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="31">
         <v>5.16</v>
       </c>
-      <c r="H35" s="30">
+      <c r="H35" s="31">
         <v>3.86</v>
       </c>
-      <c r="I35" s="30">
+      <c r="I35" s="31">
         <v>7.96</v>
       </c>
-      <c r="J35" s="30">
+      <c r="J35" s="31">
         <v>8.0</v>
       </c>
-      <c r="K35" s="30">
+      <c r="K35" s="31">
         <v>6.98</v>
       </c>
-      <c r="L35" s="30">
+      <c r="L35" s="31">
         <v>8.28</v>
       </c>
-      <c r="M35" s="30">
+      <c r="M35" s="31">
         <v>11.14</v>
       </c>
-      <c r="N35" s="30">
+      <c r="N35" s="31">
         <v>11.27</v>
       </c>
-      <c r="O35" s="30">
+      <c r="O35" s="31">
         <v>3.82</v>
       </c>
-      <c r="P35" s="30">
+      <c r="P35" s="31">
         <v>5.62</v>
       </c>
-      <c r="Q35" s="30">
+      <c r="Q35" s="31">
         <v>1.98</v>
       </c>
-      <c r="R35" s="30">
+      <c r="R35" s="31">
         <v>1.58</v>
       </c>
-      <c r="S35" s="30">
+      <c r="S35" s="31">
         <v>3.48</v>
       </c>
-      <c r="T35" s="30">
+      <c r="T35" s="31">
         <v>8.34</v>
       </c>
-      <c r="U35" s="30">
+      <c r="U35" s="31">
         <v>3.47</v>
       </c>
-      <c r="V35" s="31"/>
-      <c r="W35" s="31"/>
-      <c r="X35" s="31"/>
-      <c r="Y35" s="31"/>
+      <c r="V35" s="32"/>
+      <c r="W35" s="32"/>
+      <c r="X35" s="32"/>
+      <c r="Y35" s="32"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="28" t="s">
-        <v>347</v>
-      </c>
-      <c r="B36" s="30">
+      <c r="A36" s="29" t="s">
+        <v>348</v>
+      </c>
+      <c r="B36" s="31">
         <v>11.14</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="31">
         <v>13.29</v>
       </c>
-      <c r="D36" s="30">
+      <c r="D36" s="31">
         <v>14.74</v>
       </c>
-      <c r="E36" s="30">
+      <c r="E36" s="31">
         <v>14.99</v>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="31">
         <v>11.1</v>
       </c>
-      <c r="G36" s="30">
+      <c r="G36" s="31">
         <v>6.6</v>
       </c>
-      <c r="H36" s="30">
+      <c r="H36" s="31">
         <v>7.29</v>
       </c>
-      <c r="I36" s="30">
+      <c r="I36" s="31">
         <v>8.22</v>
       </c>
-      <c r="J36" s="30">
+      <c r="J36" s="31">
         <v>8.48</v>
       </c>
-      <c r="K36" s="30">
+      <c r="K36" s="31">
         <v>7.66</v>
       </c>
-      <c r="L36" s="30">
+      <c r="L36" s="31">
         <v>7.43</v>
       </c>
-      <c r="M36" s="30">
+      <c r="M36" s="31">
         <v>5.07</v>
       </c>
-      <c r="N36" s="30">
+      <c r="N36" s="31">
         <v>2.74</v>
       </c>
-      <c r="O36" s="30">
+      <c r="O36" s="31">
         <v>2.84</v>
       </c>
-      <c r="P36" s="30">
+      <c r="P36" s="31">
         <v>3.93</v>
       </c>
-      <c r="Q36" s="30">
+      <c r="Q36" s="31">
         <v>3.76</v>
       </c>
-      <c r="R36" s="31"/>
-      <c r="S36" s="31"/>
-      <c r="T36" s="31"/>
-      <c r="U36" s="31"/>
-      <c r="V36" s="31"/>
-      <c r="W36" s="31"/>
-      <c r="X36" s="31"/>
-      <c r="Y36" s="31"/>
+      <c r="R36" s="32"/>
+      <c r="S36" s="32"/>
+      <c r="T36" s="32"/>
+      <c r="U36" s="32"/>
+      <c r="V36" s="32"/>
+      <c r="W36" s="32"/>
+      <c r="X36" s="32"/>
+      <c r="Y36" s="32"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="26" t="s">
-        <v>348</v>
-      </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="27"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="27"/>
-      <c r="S37" s="27"/>
-      <c r="T37" s="27"/>
-      <c r="U37" s="27"/>
-      <c r="V37" s="27"/>
-      <c r="W37" s="27"/>
-      <c r="X37" s="27"/>
-      <c r="Y37" s="27"/>
+      <c r="A37" s="27" t="s">
+        <v>349</v>
+      </c>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="28"/>
+      <c r="V37" s="28"/>
+      <c r="W37" s="28"/>
+      <c r="X37" s="28"/>
+      <c r="Y37" s="28"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="28" t="s">
-        <v>349</v>
-      </c>
-      <c r="B38" s="30">
+      <c r="A38" s="29" t="s">
+        <v>350</v>
+      </c>
+      <c r="B38" s="31">
         <v>6.52</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C38" s="31">
         <v>17.91</v>
       </c>
-      <c r="D38" s="30">
+      <c r="D38" s="31">
         <v>26.37</v>
       </c>
-      <c r="E38" s="30">
+      <c r="E38" s="31">
         <v>37.13</v>
       </c>
-      <c r="F38" s="30">
+      <c r="F38" s="31">
         <v>33.43</v>
       </c>
-      <c r="G38" s="30">
+      <c r="G38" s="31">
         <v>5.08</v>
       </c>
-      <c r="H38" s="30">
+      <c r="H38" s="31">
         <v>2.49</v>
       </c>
-      <c r="I38" s="30">
+      <c r="I38" s="31">
         <v>4.42</v>
       </c>
-      <c r="J38" s="30">
+      <c r="J38" s="31">
         <v>6.91</v>
       </c>
-      <c r="K38" s="30">
+      <c r="K38" s="31">
         <v>10.62</v>
       </c>
-      <c r="L38" s="30">
+      <c r="L38" s="31">
         <v>22.75</v>
       </c>
-      <c r="M38" s="30">
+      <c r="M38" s="31">
         <v>17.6</v>
       </c>
-      <c r="N38" s="30">
+      <c r="N38" s="31">
         <v>7.94</v>
       </c>
-      <c r="O38" s="30">
+      <c r="O38" s="31">
         <v>6.38</v>
       </c>
-      <c r="P38" s="30">
+      <c r="P38" s="31">
         <v>6.97</v>
       </c>
-      <c r="Q38" s="30">
+      <c r="Q38" s="31">
         <v>4.99</v>
       </c>
-      <c r="R38" s="30">
+      <c r="R38" s="31">
         <v>4.9</v>
       </c>
-      <c r="S38" s="30">
+      <c r="S38" s="31">
         <v>14.87</v>
       </c>
-      <c r="T38" s="30">
+      <c r="T38" s="31">
         <v>12.31</v>
       </c>
-      <c r="U38" s="30">
+      <c r="U38" s="31">
         <v>5.52</v>
       </c>
-      <c r="V38" s="31"/>
-      <c r="W38" s="31"/>
-      <c r="X38" s="31"/>
-      <c r="Y38" s="31"/>
+      <c r="V38" s="32"/>
+      <c r="W38" s="32"/>
+      <c r="X38" s="32"/>
+      <c r="Y38" s="32"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="28" t="s">
-        <v>350</v>
-      </c>
-      <c r="B39" s="30">
+      <c r="A39" s="29" t="s">
+        <v>351</v>
+      </c>
+      <c r="B39" s="31">
         <v>24.65</v>
       </c>
-      <c r="C39" s="30">
+      <c r="C39" s="31">
         <v>26.46</v>
       </c>
-      <c r="D39" s="30">
+      <c r="D39" s="31">
         <v>25.01</v>
       </c>
-      <c r="E39" s="30">
+      <c r="E39" s="31">
         <v>20.8</v>
       </c>
-      <c r="F39" s="30">
+      <c r="F39" s="31">
         <v>12.14</v>
       </c>
-      <c r="G39" s="30">
+      <c r="G39" s="31">
         <v>5.83</v>
       </c>
-      <c r="H39" s="30">
+      <c r="H39" s="31">
         <v>7.95</v>
       </c>
-      <c r="I39" s="30">
+      <c r="I39" s="31">
         <v>10.27</v>
       </c>
-      <c r="J39" s="30">
+      <c r="J39" s="31">
         <v>11.72</v>
       </c>
-      <c r="K39" s="30">
+      <c r="K39" s="31">
         <v>12.59</v>
       </c>
-      <c r="L39" s="30">
+      <c r="L39" s="31">
         <v>11.67</v>
       </c>
-      <c r="M39" s="30">
+      <c r="M39" s="31">
         <v>8.02</v>
       </c>
-      <c r="N39" s="30">
+      <c r="N39" s="31">
         <v>5.9</v>
       </c>
-      <c r="O39" s="30">
+      <c r="O39" s="31">
         <v>8.24</v>
       </c>
-      <c r="P39" s="30">
+      <c r="P39" s="31">
         <v>9.84</v>
       </c>
-      <c r="Q39" s="30">
+      <c r="Q39" s="31">
         <v>8.76</v>
       </c>
-      <c r="R39" s="31"/>
-      <c r="S39" s="31"/>
-      <c r="T39" s="31"/>
-      <c r="U39" s="31"/>
-      <c r="V39" s="31"/>
-      <c r="W39" s="31"/>
-      <c r="X39" s="31"/>
-      <c r="Y39" s="31"/>
+      <c r="R39" s="32"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="32"/>
+      <c r="U39" s="32"/>
+      <c r="V39" s="32"/>
+      <c r="W39" s="32"/>
+      <c r="X39" s="32"/>
+      <c r="Y39" s="32"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="26" t="s">
-        <v>351</v>
-      </c>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
-      <c r="N40" s="27"/>
-      <c r="O40" s="27"/>
-      <c r="P40" s="27"/>
-      <c r="Q40" s="27"/>
-      <c r="R40" s="27"/>
-      <c r="S40" s="27"/>
-      <c r="T40" s="27"/>
-      <c r="U40" s="27"/>
-      <c r="V40" s="27"/>
-      <c r="W40" s="27"/>
-      <c r="X40" s="27"/>
-      <c r="Y40" s="27"/>
+      <c r="A40" s="27" t="s">
+        <v>352</v>
+      </c>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
+      <c r="S40" s="28"/>
+      <c r="T40" s="28"/>
+      <c r="U40" s="28"/>
+      <c r="V40" s="28"/>
+      <c r="W40" s="28"/>
+      <c r="X40" s="28"/>
+      <c r="Y40" s="28"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="28" t="s">
-        <v>352</v>
-      </c>
-      <c r="B41" s="31"/>
-      <c r="C41" s="29">
+      <c r="A41" s="29" t="s">
+        <v>353</v>
+      </c>
+      <c r="B41" s="32"/>
+      <c r="C41" s="30">
         <v>448.75</v>
       </c>
-      <c r="D41" s="30">
+      <c r="D41" s="31">
         <v>79.5</v>
       </c>
-      <c r="E41" s="30">
+      <c r="E41" s="31">
         <v>74.99</v>
       </c>
-      <c r="F41" s="30">
+      <c r="F41" s="31">
         <v>69.69</v>
       </c>
-      <c r="G41" s="29">
+      <c r="G41" s="30">
         <v>110.97</v>
       </c>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
-      <c r="K41" s="31"/>
-      <c r="L41" s="31"/>
-      <c r="M41" s="31"/>
-      <c r="N41" s="31"/>
-      <c r="O41" s="31"/>
-      <c r="P41" s="31"/>
-      <c r="Q41" s="31"/>
-      <c r="R41" s="31"/>
-      <c r="S41" s="31"/>
-      <c r="T41" s="31"/>
-      <c r="U41" s="31"/>
-      <c r="V41" s="31"/>
-      <c r="W41" s="31"/>
-      <c r="X41" s="31"/>
-      <c r="Y41" s="31"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="32"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="32"/>
+      <c r="L41" s="32"/>
+      <c r="M41" s="32"/>
+      <c r="N41" s="32"/>
+      <c r="O41" s="32"/>
+      <c r="P41" s="32"/>
+      <c r="Q41" s="32"/>
+      <c r="R41" s="32"/>
+      <c r="S41" s="32"/>
+      <c r="T41" s="32"/>
+      <c r="U41" s="32"/>
+      <c r="V41" s="32"/>
+      <c r="W41" s="32"/>
+      <c r="X41" s="32"/>
+      <c r="Y41" s="32"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="28" t="s">
-        <v>353</v>
-      </c>
-      <c r="B42" s="30">
+      <c r="A42" s="29" t="s">
+        <v>354</v>
+      </c>
+      <c r="B42" s="31">
         <v>94.87</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C42" s="31">
         <v>86.15</v>
       </c>
-      <c r="D42" s="30">
+      <c r="D42" s="31">
         <v>87.53</v>
       </c>
-      <c r="E42" s="29">
+      <c r="E42" s="30">
         <v>144.36</v>
       </c>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="31"/>
-      <c r="L42" s="31"/>
-      <c r="M42" s="31"/>
-      <c r="N42" s="31"/>
-      <c r="O42" s="31"/>
-      <c r="P42" s="31"/>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="31"/>
-      <c r="S42" s="31"/>
-      <c r="T42" s="31"/>
-      <c r="U42" s="31"/>
-      <c r="V42" s="31"/>
-      <c r="W42" s="31"/>
-      <c r="X42" s="31"/>
-      <c r="Y42" s="31"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="32"/>
+      <c r="Q42" s="32"/>
+      <c r="R42" s="32"/>
+      <c r="S42" s="32"/>
+      <c r="T42" s="32"/>
+      <c r="U42" s="32"/>
+      <c r="V42" s="32"/>
+      <c r="W42" s="32"/>
+      <c r="X42" s="32"/>
+      <c r="Y42" s="32"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="26" t="s">
-        <v>354</v>
-      </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="27"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="27"/>
-      <c r="P43" s="27"/>
-      <c r="Q43" s="27"/>
-      <c r="R43" s="27"/>
-      <c r="S43" s="27"/>
-      <c r="T43" s="27"/>
-      <c r="U43" s="27"/>
-      <c r="V43" s="27"/>
-      <c r="W43" s="27"/>
-      <c r="X43" s="27"/>
-      <c r="Y43" s="27"/>
+      <c r="A43" s="27" t="s">
+        <v>355</v>
+      </c>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
+      <c r="R43" s="28"/>
+      <c r="S43" s="28"/>
+      <c r="T43" s="28"/>
+      <c r="U43" s="28"/>
+      <c r="V43" s="28"/>
+      <c r="W43" s="28"/>
+      <c r="X43" s="28"/>
+      <c r="Y43" s="28"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="28" t="s">
-        <v>355</v>
-      </c>
-      <c r="B44" s="30">
+      <c r="A44" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="B44" s="31">
         <v>45.18</v>
       </c>
-      <c r="C44" s="30">
+      <c r="C44" s="31">
         <v>82.53</v>
       </c>
-      <c r="D44" s="30">
+      <c r="D44" s="31">
         <v>95.35</v>
       </c>
-      <c r="E44" s="30">
+      <c r="E44" s="31">
         <v>95.86</v>
       </c>
-      <c r="F44" s="30">
+      <c r="F44" s="31">
         <v>39.55</v>
       </c>
-      <c r="G44" s="30">
+      <c r="G44" s="31">
         <v>50.87</v>
       </c>
-      <c r="H44" s="31"/>
-      <c r="I44" s="31"/>
-      <c r="J44" s="31"/>
-      <c r="K44" s="31"/>
-      <c r="L44" s="31"/>
-      <c r="M44" s="31"/>
-      <c r="N44" s="31"/>
-      <c r="O44" s="31"/>
-      <c r="P44" s="31"/>
-      <c r="Q44" s="31"/>
-      <c r="R44" s="31"/>
-      <c r="S44" s="31"/>
-      <c r="T44" s="31"/>
-      <c r="U44" s="31"/>
-      <c r="V44" s="31"/>
-      <c r="W44" s="31"/>
-      <c r="X44" s="31"/>
-      <c r="Y44" s="31"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="32"/>
+      <c r="L44" s="32"/>
+      <c r="M44" s="32"/>
+      <c r="N44" s="32"/>
+      <c r="O44" s="32"/>
+      <c r="P44" s="32"/>
+      <c r="Q44" s="32"/>
+      <c r="R44" s="32"/>
+      <c r="S44" s="32"/>
+      <c r="T44" s="32"/>
+      <c r="U44" s="32"/>
+      <c r="V44" s="32"/>
+      <c r="W44" s="32"/>
+      <c r="X44" s="32"/>
+      <c r="Y44" s="32"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="28" t="s">
-        <v>356</v>
-      </c>
-      <c r="B45" s="30">
+      <c r="A45" s="29" t="s">
+        <v>357</v>
+      </c>
+      <c r="B45" s="31">
         <v>68.67</v>
       </c>
-      <c r="C45" s="30">
+      <c r="C45" s="31">
         <v>70.01</v>
       </c>
-      <c r="D45" s="30">
+      <c r="D45" s="31">
         <v>73.39</v>
       </c>
-      <c r="E45" s="30">
+      <c r="E45" s="31">
         <v>87.79</v>
       </c>
-      <c r="F45" s="29">
+      <c r="F45" s="30">
         <v>159.14</v>
       </c>
-      <c r="G45" s="31"/>
-      <c r="H45" s="31"/>
-      <c r="I45" s="31"/>
-      <c r="J45" s="31"/>
-      <c r="K45" s="31"/>
-      <c r="L45" s="31"/>
-      <c r="M45" s="31"/>
-      <c r="N45" s="31"/>
-      <c r="O45" s="31"/>
-      <c r="P45" s="31"/>
-      <c r="Q45" s="31"/>
-      <c r="R45" s="31"/>
-      <c r="S45" s="31"/>
-      <c r="T45" s="31"/>
-      <c r="U45" s="31"/>
-      <c r="V45" s="31"/>
-      <c r="W45" s="31"/>
-      <c r="X45" s="31"/>
-      <c r="Y45" s="31"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="32"/>
+      <c r="K45" s="32"/>
+      <c r="L45" s="32"/>
+      <c r="M45" s="32"/>
+      <c r="N45" s="32"/>
+      <c r="O45" s="32"/>
+      <c r="P45" s="32"/>
+      <c r="Q45" s="32"/>
+      <c r="R45" s="32"/>
+      <c r="S45" s="32"/>
+      <c r="T45" s="32"/>
+      <c r="U45" s="32"/>
+      <c r="V45" s="32"/>
+      <c r="W45" s="32"/>
+      <c r="X45" s="32"/>
+      <c r="Y45" s="32"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="26" t="s">
-        <v>357</v>
-      </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="27"/>
-      <c r="N46" s="27"/>
-      <c r="O46" s="27"/>
-      <c r="P46" s="27"/>
-      <c r="Q46" s="27"/>
-      <c r="R46" s="27"/>
-      <c r="S46" s="27"/>
-      <c r="T46" s="27"/>
-      <c r="U46" s="27"/>
-      <c r="V46" s="27"/>
-      <c r="W46" s="27"/>
-      <c r="X46" s="27"/>
-      <c r="Y46" s="27"/>
+      <c r="A46" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="28"/>
+      <c r="O46" s="28"/>
+      <c r="P46" s="28"/>
+      <c r="Q46" s="28"/>
+      <c r="R46" s="28"/>
+      <c r="S46" s="28"/>
+      <c r="T46" s="28"/>
+      <c r="U46" s="28"/>
+      <c r="V46" s="28"/>
+      <c r="W46" s="28"/>
+      <c r="X46" s="28"/>
+      <c r="Y46" s="28"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="28" t="s">
-        <v>358</v>
-      </c>
-      <c r="B47" s="30">
+      <c r="A47" s="29" t="s">
+        <v>359</v>
+      </c>
+      <c r="B47" s="31">
         <v>80.28</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="30">
         <v>109.64</v>
       </c>
-      <c r="D47" s="29">
+      <c r="D47" s="30">
         <v>109.92</v>
       </c>
-      <c r="E47" s="29">
+      <c r="E47" s="30">
         <v>102.46</v>
       </c>
-      <c r="F47" s="30">
+      <c r="F47" s="31">
         <v>42.35</v>
       </c>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
-      <c r="K47" s="31"/>
-      <c r="L47" s="31"/>
-      <c r="M47" s="31"/>
-      <c r="N47" s="31"/>
-      <c r="O47" s="31"/>
-      <c r="P47" s="31"/>
-      <c r="Q47" s="31"/>
-      <c r="R47" s="31"/>
-      <c r="S47" s="31"/>
-      <c r="T47" s="31"/>
-      <c r="U47" s="31"/>
-      <c r="V47" s="31"/>
-      <c r="W47" s="31"/>
-      <c r="X47" s="31"/>
-      <c r="Y47" s="31"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="32"/>
+      <c r="K47" s="32"/>
+      <c r="L47" s="32"/>
+      <c r="M47" s="32"/>
+      <c r="N47" s="32"/>
+      <c r="O47" s="32"/>
+      <c r="P47" s="32"/>
+      <c r="Q47" s="32"/>
+      <c r="R47" s="32"/>
+      <c r="S47" s="32"/>
+      <c r="T47" s="32"/>
+      <c r="U47" s="32"/>
+      <c r="V47" s="32"/>
+      <c r="W47" s="32"/>
+      <c r="X47" s="32"/>
+      <c r="Y47" s="32"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="28" t="s">
-        <v>359</v>
-      </c>
-      <c r="B48" s="30">
+      <c r="A48" s="29" t="s">
+        <v>360</v>
+      </c>
+      <c r="B48" s="31">
         <v>78.61</v>
       </c>
-      <c r="C48" s="30">
+      <c r="C48" s="31">
         <v>80.4</v>
       </c>
-      <c r="D48" s="30">
+      <c r="D48" s="31">
         <v>86.38</v>
       </c>
-      <c r="E48" s="29">
+      <c r="E48" s="30">
         <v>112.76</v>
       </c>
-      <c r="F48" s="29">
+      <c r="F48" s="30">
         <v>611.86</v>
       </c>
-      <c r="G48" s="31"/>
-      <c r="H48" s="31"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="31"/>
-      <c r="K48" s="31"/>
-      <c r="L48" s="31"/>
-      <c r="M48" s="31"/>
-      <c r="N48" s="31"/>
-      <c r="O48" s="31"/>
-      <c r="P48" s="31"/>
-      <c r="Q48" s="31"/>
-      <c r="R48" s="31"/>
-      <c r="S48" s="31"/>
-      <c r="T48" s="31"/>
-      <c r="U48" s="31"/>
-      <c r="V48" s="31"/>
-      <c r="W48" s="31"/>
-      <c r="X48" s="31"/>
-      <c r="Y48" s="31"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="32"/>
+      <c r="K48" s="32"/>
+      <c r="L48" s="32"/>
+      <c r="M48" s="32"/>
+      <c r="N48" s="32"/>
+      <c r="O48" s="32"/>
+      <c r="P48" s="32"/>
+      <c r="Q48" s="32"/>
+      <c r="R48" s="32"/>
+      <c r="S48" s="32"/>
+      <c r="T48" s="32"/>
+      <c r="U48" s="32"/>
+      <c r="V48" s="32"/>
+      <c r="W48" s="32"/>
+      <c r="X48" s="32"/>
+      <c r="Y48" s="32"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="26" t="s">
-        <v>360</v>
-      </c>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27"/>
-      <c r="N49" s="27"/>
-      <c r="O49" s="27"/>
-      <c r="P49" s="27"/>
-      <c r="Q49" s="27"/>
-      <c r="R49" s="27"/>
-      <c r="S49" s="27"/>
-      <c r="T49" s="27"/>
-      <c r="U49" s="27"/>
-      <c r="V49" s="27"/>
-      <c r="W49" s="27"/>
-      <c r="X49" s="27"/>
-      <c r="Y49" s="27"/>
+      <c r="A49" s="27" t="s">
+        <v>361</v>
+      </c>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="28"/>
+      <c r="P49" s="28"/>
+      <c r="Q49" s="28"/>
+      <c r="R49" s="28"/>
+      <c r="S49" s="28"/>
+      <c r="T49" s="28"/>
+      <c r="U49" s="28"/>
+      <c r="V49" s="28"/>
+      <c r="W49" s="28"/>
+      <c r="X49" s="28"/>
+      <c r="Y49" s="28"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="28" t="s">
-        <v>361</v>
-      </c>
-      <c r="B50" s="29">
+      <c r="A50" s="29" t="s">
+        <v>362</v>
+      </c>
+      <c r="B50" s="30">
         <v>176.81</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="30">
         <v>120.88</v>
       </c>
-      <c r="D50" s="29">
+      <c r="D50" s="30">
         <v>202.25</v>
       </c>
-      <c r="E50" s="29">
+      <c r="E50" s="30">
         <v>360.54</v>
       </c>
-      <c r="F50" s="30">
+      <c r="F50" s="31">
         <v>65.15</v>
       </c>
-      <c r="G50" s="31"/>
-      <c r="H50" s="31"/>
-      <c r="I50" s="31"/>
-      <c r="J50" s="31"/>
-      <c r="K50" s="31"/>
-      <c r="L50" s="31"/>
-      <c r="M50" s="31"/>
-      <c r="N50" s="31"/>
-      <c r="O50" s="31"/>
-      <c r="P50" s="31"/>
-      <c r="Q50" s="31"/>
-      <c r="R50" s="31"/>
-      <c r="S50" s="31"/>
-      <c r="T50" s="31"/>
-      <c r="U50" s="31"/>
-      <c r="V50" s="31"/>
-      <c r="W50" s="31"/>
-      <c r="X50" s="31"/>
-      <c r="Y50" s="31"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="32"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="32"/>
+      <c r="M50" s="32"/>
+      <c r="N50" s="32"/>
+      <c r="O50" s="32"/>
+      <c r="P50" s="32"/>
+      <c r="Q50" s="32"/>
+      <c r="R50" s="32"/>
+      <c r="S50" s="32"/>
+      <c r="T50" s="32"/>
+      <c r="U50" s="32"/>
+      <c r="V50" s="32"/>
+      <c r="W50" s="32"/>
+      <c r="X50" s="32"/>
+      <c r="Y50" s="32"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="28" t="s">
-        <v>362</v>
-      </c>
-      <c r="B51" s="30">
+      <c r="A51" s="29" t="s">
+        <v>363</v>
+      </c>
+      <c r="B51" s="31">
         <v>10.56</v>
       </c>
-      <c r="C51" s="30">
+      <c r="C51" s="31">
         <v>12.82</v>
       </c>
-      <c r="D51" s="30">
+      <c r="D51" s="31">
         <v>14.38</v>
       </c>
-      <c r="E51" s="30">
+      <c r="E51" s="31">
         <v>14.52</v>
       </c>
-      <c r="F51" s="30">
+      <c r="F51" s="31">
         <v>10.5</v>
       </c>
-      <c r="G51" s="30">
+      <c r="G51" s="31">
         <v>6.02</v>
       </c>
-      <c r="H51" s="30">
+      <c r="H51" s="31">
         <v>6.66</v>
       </c>
-      <c r="I51" s="30">
+      <c r="I51" s="31">
         <v>7.52</v>
       </c>
-      <c r="J51" s="30">
+      <c r="J51" s="31">
         <v>7.69</v>
       </c>
-      <c r="K51" s="30">
+      <c r="K51" s="31">
         <v>6.88</v>
       </c>
-      <c r="L51" s="30">
+      <c r="L51" s="31">
         <v>6.61</v>
       </c>
-      <c r="M51" s="30">
+      <c r="M51" s="31">
         <v>4.58</v>
       </c>
-      <c r="N51" s="30">
+      <c r="N51" s="31">
         <v>2.61</v>
       </c>
-      <c r="O51" s="30">
+      <c r="O51" s="31">
         <v>2.77</v>
       </c>
-      <c r="P51" s="30">
+      <c r="P51" s="31">
         <v>3.88</v>
       </c>
-      <c r="Q51" s="30">
+      <c r="Q51" s="31">
         <v>3.73</v>
       </c>
-      <c r="R51" s="31"/>
-      <c r="S51" s="31"/>
-      <c r="T51" s="31"/>
-      <c r="U51" s="31"/>
-      <c r="V51" s="31"/>
-      <c r="W51" s="31"/>
-      <c r="X51" s="31"/>
-      <c r="Y51" s="31"/>
+      <c r="R51" s="32"/>
+      <c r="S51" s="32"/>
+      <c r="T51" s="32"/>
+      <c r="U51" s="32"/>
+      <c r="V51" s="32"/>
+      <c r="W51" s="32"/>
+      <c r="X51" s="32"/>
+      <c r="Y51" s="32"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="26" t="s">
-        <v>363</v>
-      </c>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="27"/>
-      <c r="J52" s="27"/>
-      <c r="K52" s="27"/>
-      <c r="L52" s="27"/>
-      <c r="M52" s="27"/>
-      <c r="N52" s="27"/>
-      <c r="O52" s="27"/>
-      <c r="P52" s="27"/>
-      <c r="Q52" s="27"/>
-      <c r="R52" s="27"/>
-      <c r="S52" s="27"/>
-      <c r="T52" s="27"/>
-      <c r="U52" s="27"/>
-      <c r="V52" s="27"/>
-      <c r="W52" s="27"/>
-      <c r="X52" s="27"/>
-      <c r="Y52" s="27"/>
+      <c r="A52" s="27" t="s">
+        <v>364</v>
+      </c>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="28"/>
+      <c r="R52" s="28"/>
+      <c r="S52" s="28"/>
+      <c r="T52" s="28"/>
+      <c r="U52" s="28"/>
+      <c r="V52" s="28"/>
+      <c r="W52" s="28"/>
+      <c r="X52" s="28"/>
+      <c r="Y52" s="28"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="28" t="s">
-        <v>364</v>
-      </c>
-      <c r="B53" s="34">
+      <c r="A53" s="29" t="s">
+        <v>365</v>
+      </c>
+      <c r="B53" s="35">
         <v>-1.42</v>
       </c>
-      <c r="C53" s="34">
+      <c r="C53" s="35">
         <v>-2.66</v>
       </c>
-      <c r="D53" s="34">
+      <c r="D53" s="35">
         <v>-3.8</v>
       </c>
-      <c r="E53" s="34">
+      <c r="E53" s="35">
         <v>-2.63</v>
       </c>
-      <c r="F53" s="30">
+      <c r="F53" s="31">
         <v>0.01</v>
       </c>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="31"/>
-      <c r="K53" s="31"/>
-      <c r="L53" s="31"/>
-      <c r="M53" s="31"/>
-      <c r="N53" s="31"/>
-      <c r="O53" s="31"/>
-      <c r="P53" s="31"/>
-      <c r="Q53" s="31"/>
-      <c r="R53" s="31"/>
-      <c r="S53" s="31"/>
-      <c r="T53" s="31"/>
-      <c r="U53" s="31"/>
-      <c r="V53" s="31"/>
-      <c r="W53" s="31"/>
-      <c r="X53" s="31"/>
-      <c r="Y53" s="31"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="32"/>
+      <c r="L53" s="32"/>
+      <c r="M53" s="32"/>
+      <c r="N53" s="32"/>
+      <c r="O53" s="32"/>
+      <c r="P53" s="32"/>
+      <c r="Q53" s="32"/>
+      <c r="R53" s="32"/>
+      <c r="S53" s="32"/>
+      <c r="T53" s="32"/>
+      <c r="U53" s="32"/>
+      <c r="V53" s="32"/>
+      <c r="W53" s="32"/>
+      <c r="X53" s="32"/>
+      <c r="Y53" s="32"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="26" t="s">
-        <v>365</v>
-      </c>
-      <c r="B54" s="27"/>
-      <c r="C54" s="27"/>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
-      <c r="H54" s="27"/>
-      <c r="I54" s="27"/>
-      <c r="J54" s="27"/>
-      <c r="K54" s="27"/>
-      <c r="L54" s="27"/>
-      <c r="M54" s="27"/>
-      <c r="N54" s="27"/>
-      <c r="O54" s="27"/>
-      <c r="P54" s="27"/>
-      <c r="Q54" s="27"/>
-      <c r="R54" s="27"/>
-      <c r="S54" s="27"/>
-      <c r="T54" s="27"/>
-      <c r="U54" s="27"/>
-      <c r="V54" s="27"/>
-      <c r="W54" s="27"/>
-      <c r="X54" s="27"/>
-      <c r="Y54" s="27"/>
+      <c r="A54" s="27" t="s">
+        <v>366</v>
+      </c>
+      <c r="B54" s="28"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="28"/>
+      <c r="J54" s="28"/>
+      <c r="K54" s="28"/>
+      <c r="L54" s="28"/>
+      <c r="M54" s="28"/>
+      <c r="N54" s="28"/>
+      <c r="O54" s="28"/>
+      <c r="P54" s="28"/>
+      <c r="Q54" s="28"/>
+      <c r="R54" s="28"/>
+      <c r="S54" s="28"/>
+      <c r="T54" s="28"/>
+      <c r="U54" s="28"/>
+      <c r="V54" s="28"/>
+      <c r="W54" s="28"/>
+      <c r="X54" s="28"/>
+      <c r="Y54" s="28"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="28" t="s">
-        <v>366</v>
-      </c>
-      <c r="B55" s="30">
+      <c r="A55" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="B55" s="31">
         <v>4.97</v>
       </c>
-      <c r="C55" s="30">
+      <c r="C55" s="31">
         <v>16.55</v>
       </c>
-      <c r="D55" s="30">
+      <c r="D55" s="31">
         <v>24.77</v>
       </c>
-      <c r="E55" s="30">
+      <c r="E55" s="31">
         <v>35.57</v>
       </c>
-      <c r="F55" s="30">
+      <c r="F55" s="31">
         <v>31.54</v>
       </c>
-      <c r="G55" s="30">
+      <c r="G55" s="31">
         <v>4.77</v>
       </c>
-      <c r="H55" s="30">
+      <c r="H55" s="31">
         <v>2.35</v>
       </c>
-      <c r="I55" s="30">
+      <c r="I55" s="31">
         <v>3.97</v>
       </c>
-      <c r="J55" s="30">
+      <c r="J55" s="31">
         <v>6.11</v>
       </c>
-      <c r="K55" s="30">
+      <c r="K55" s="31">
         <v>9.18</v>
       </c>
-      <c r="L55" s="30">
+      <c r="L55" s="31">
         <v>20.71</v>
       </c>
-      <c r="M55" s="30">
+      <c r="M55" s="31">
         <v>16.69</v>
       </c>
-      <c r="N55" s="30">
+      <c r="N55" s="31">
         <v>7.56</v>
       </c>
-      <c r="O55" s="30">
+      <c r="O55" s="31">
         <v>4.95</v>
       </c>
-      <c r="P55" s="30">
+      <c r="P55" s="31">
         <v>5.72</v>
       </c>
-      <c r="Q55" s="30">
+      <c r="Q55" s="31">
         <v>2.95</v>
       </c>
-      <c r="R55" s="30">
+      <c r="R55" s="31">
         <v>2.51</v>
       </c>
-      <c r="S55" s="30">
+      <c r="S55" s="31">
         <v>12.53</v>
       </c>
-      <c r="T55" s="30">
+      <c r="T55" s="31">
         <v>11.79</v>
       </c>
-      <c r="U55" s="30">
+      <c r="U55" s="31">
         <v>5.24</v>
       </c>
-      <c r="V55" s="31"/>
-      <c r="W55" s="31"/>
-      <c r="X55" s="31"/>
-      <c r="Y55" s="31"/>
+      <c r="V55" s="32"/>
+      <c r="W55" s="32"/>
+      <c r="X55" s="32"/>
+      <c r="Y55" s="32"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="28" t="s">
-        <v>367</v>
-      </c>
-      <c r="B56" s="30">
+      <c r="A56" s="29" t="s">
+        <v>368</v>
+      </c>
+      <c r="B56" s="31">
         <v>23.0</v>
       </c>
-      <c r="C56" s="30">
+      <c r="C56" s="31">
         <v>25.03</v>
       </c>
-      <c r="D56" s="30">
+      <c r="D56" s="31">
         <v>23.95</v>
       </c>
-      <c r="E56" s="30">
+      <c r="E56" s="31">
         <v>20.34</v>
       </c>
-      <c r="F56" s="30">
+      <c r="F56" s="31">
         <v>11.7</v>
       </c>
-      <c r="G56" s="30">
+      <c r="G56" s="31">
         <v>5.15</v>
       </c>
-      <c r="H56" s="30">
+      <c r="H56" s="31">
         <v>6.97</v>
       </c>
-      <c r="I56" s="30">
+      <c r="I56" s="31">
         <v>9.09</v>
       </c>
-      <c r="J56" s="30">
+      <c r="J56" s="31">
         <v>10.62</v>
       </c>
-      <c r="K56" s="30">
+      <c r="K56" s="31">
         <v>11.89</v>
       </c>
-      <c r="L56" s="30">
+      <c r="L56" s="31">
         <v>11.77</v>
       </c>
-      <c r="M56" s="30">
+      <c r="M56" s="31">
         <v>7.41</v>
       </c>
-      <c r="N56" s="30">
+      <c r="N56" s="31">
         <v>4.28</v>
       </c>
-      <c r="O56" s="30">
+      <c r="O56" s="31">
         <v>6.07</v>
       </c>
-      <c r="P56" s="30">
+      <c r="P56" s="31">
         <v>8.08</v>
       </c>
-      <c r="Q56" s="30">
+      <c r="Q56" s="31">
         <v>7.56</v>
       </c>
-      <c r="R56" s="31"/>
-      <c r="S56" s="31"/>
-      <c r="T56" s="31"/>
-      <c r="U56" s="31"/>
-      <c r="V56" s="31"/>
-      <c r="W56" s="31"/>
-      <c r="X56" s="31"/>
-      <c r="Y56" s="31"/>
+      <c r="R56" s="32"/>
+      <c r="S56" s="32"/>
+      <c r="T56" s="32"/>
+      <c r="U56" s="32"/>
+      <c r="V56" s="32"/>
+      <c r="W56" s="32"/>
+      <c r="X56" s="32"/>
+      <c r="Y56" s="32"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="26" t="s">
-        <v>368</v>
-      </c>
-      <c r="B57" s="27"/>
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="27"/>
-      <c r="I57" s="27"/>
-      <c r="J57" s="27"/>
-      <c r="K57" s="27"/>
-      <c r="L57" s="27"/>
-      <c r="M57" s="27"/>
-      <c r="N57" s="27"/>
-      <c r="O57" s="27"/>
-      <c r="P57" s="27"/>
-      <c r="Q57" s="27"/>
-      <c r="R57" s="27"/>
-      <c r="S57" s="27"/>
-      <c r="T57" s="27"/>
-      <c r="U57" s="27"/>
-      <c r="V57" s="27"/>
-      <c r="W57" s="27"/>
-      <c r="X57" s="27"/>
-      <c r="Y57" s="27"/>
+      <c r="A57" s="27" t="s">
+        <v>369</v>
+      </c>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="28"/>
+      <c r="K57" s="28"/>
+      <c r="L57" s="28"/>
+      <c r="M57" s="28"/>
+      <c r="N57" s="28"/>
+      <c r="O57" s="28"/>
+      <c r="P57" s="28"/>
+      <c r="Q57" s="28"/>
+      <c r="R57" s="28"/>
+      <c r="S57" s="28"/>
+      <c r="T57" s="28"/>
+      <c r="U57" s="28"/>
+      <c r="V57" s="28"/>
+      <c r="W57" s="28"/>
+      <c r="X57" s="28"/>
+      <c r="Y57" s="28"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="28" t="s">
-        <v>369</v>
-      </c>
-      <c r="B58" s="29">
+      <c r="A58" s="29" t="s">
+        <v>370</v>
+      </c>
+      <c r="B58" s="30">
         <v>100.84</v>
       </c>
-      <c r="C58" s="30">
+      <c r="C58" s="31">
         <v>88.96</v>
       </c>
-      <c r="D58" s="29">
+      <c r="D58" s="30">
         <v>128.08</v>
       </c>
-      <c r="E58" s="29">
+      <c r="E58" s="30">
         <v>160.16</v>
       </c>
-      <c r="F58" s="29">
+      <c r="F58" s="30">
         <v>144.36</v>
       </c>
-      <c r="G58" s="30">
+      <c r="G58" s="31">
         <v>46.15</v>
       </c>
-      <c r="H58" s="31"/>
-      <c r="I58" s="31"/>
-      <c r="J58" s="31"/>
-      <c r="K58" s="31"/>
-      <c r="L58" s="31"/>
-      <c r="M58" s="31"/>
-      <c r="N58" s="31"/>
-      <c r="O58" s="31"/>
-      <c r="P58" s="31"/>
-      <c r="Q58" s="31"/>
-      <c r="R58" s="31"/>
-      <c r="S58" s="31"/>
-      <c r="T58" s="31"/>
-      <c r="U58" s="31"/>
-      <c r="V58" s="31"/>
-      <c r="W58" s="31"/>
-      <c r="X58" s="31"/>
-      <c r="Y58" s="31"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
+      <c r="L58" s="32"/>
+      <c r="M58" s="32"/>
+      <c r="N58" s="32"/>
+      <c r="O58" s="32"/>
+      <c r="P58" s="32"/>
+      <c r="Q58" s="32"/>
+      <c r="R58" s="32"/>
+      <c r="S58" s="32"/>
+      <c r="T58" s="32"/>
+      <c r="U58" s="32"/>
+      <c r="V58" s="32"/>
+      <c r="W58" s="32"/>
+      <c r="X58" s="32"/>
+      <c r="Y58" s="32"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="28" t="s">
-        <v>370</v>
-      </c>
-      <c r="B59" s="29">
+      <c r="A59" s="29" t="s">
+        <v>371</v>
+      </c>
+      <c r="B59" s="30">
         <v>130.4</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C59" s="30">
         <v>128.04</v>
       </c>
-      <c r="D59" s="29">
+      <c r="D59" s="30">
         <v>158.2</v>
       </c>
-      <c r="E59" s="29">
+      <c r="E59" s="30">
         <v>373.58</v>
       </c>
-      <c r="F59" s="31"/>
-      <c r="G59" s="31"/>
-      <c r="H59" s="31"/>
-      <c r="I59" s="31"/>
-      <c r="J59" s="31"/>
-      <c r="K59" s="31"/>
-      <c r="L59" s="31"/>
-      <c r="M59" s="31"/>
-      <c r="N59" s="31"/>
-      <c r="O59" s="31"/>
-      <c r="P59" s="31"/>
-      <c r="Q59" s="31"/>
-      <c r="R59" s="31"/>
-      <c r="S59" s="31"/>
-      <c r="T59" s="31"/>
-      <c r="U59" s="31"/>
-      <c r="V59" s="31"/>
-      <c r="W59" s="31"/>
-      <c r="X59" s="31"/>
-      <c r="Y59" s="31"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="32"/>
+      <c r="K59" s="32"/>
+      <c r="L59" s="32"/>
+      <c r="M59" s="32"/>
+      <c r="N59" s="32"/>
+      <c r="O59" s="32"/>
+      <c r="P59" s="32"/>
+      <c r="Q59" s="32"/>
+      <c r="R59" s="32"/>
+      <c r="S59" s="32"/>
+      <c r="T59" s="32"/>
+      <c r="U59" s="32"/>
+      <c r="V59" s="32"/>
+      <c r="W59" s="32"/>
+      <c r="X59" s="32"/>
+      <c r="Y59" s="32"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="B60" s="27"/>
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="27"/>
-      <c r="H60" s="27"/>
-      <c r="I60" s="27"/>
-      <c r="J60" s="27"/>
-      <c r="K60" s="27"/>
-      <c r="L60" s="27"/>
-      <c r="M60" s="27"/>
-      <c r="N60" s="27"/>
-      <c r="O60" s="27"/>
-      <c r="P60" s="27"/>
-      <c r="Q60" s="27"/>
-      <c r="R60" s="27"/>
-      <c r="S60" s="27"/>
-      <c r="T60" s="27"/>
-      <c r="U60" s="27"/>
-      <c r="V60" s="27"/>
-      <c r="W60" s="27"/>
-      <c r="X60" s="27"/>
-      <c r="Y60" s="27"/>
+      <c r="A60" s="27" t="s">
+        <v>372</v>
+      </c>
+      <c r="B60" s="28"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="28"/>
+      <c r="I60" s="28"/>
+      <c r="J60" s="28"/>
+      <c r="K60" s="28"/>
+      <c r="L60" s="28"/>
+      <c r="M60" s="28"/>
+      <c r="N60" s="28"/>
+      <c r="O60" s="28"/>
+      <c r="P60" s="28"/>
+      <c r="Q60" s="28"/>
+      <c r="R60" s="28"/>
+      <c r="S60" s="28"/>
+      <c r="T60" s="28"/>
+      <c r="U60" s="28"/>
+      <c r="V60" s="28"/>
+      <c r="W60" s="28"/>
+      <c r="X60" s="28"/>
+      <c r="Y60" s="28"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="28" t="s">
-        <v>372</v>
-      </c>
-      <c r="B61" s="29">
+      <c r="A61" s="29" t="s">
+        <v>373</v>
+      </c>
+      <c r="B61" s="30">
         <v>397.88</v>
       </c>
-      <c r="C61" s="30">
+      <c r="C61" s="31">
         <v>82.13</v>
       </c>
-      <c r="D61" s="30">
+      <c r="D61" s="31">
         <v>58.64</v>
       </c>
-      <c r="E61" s="30">
+      <c r="E61" s="31">
         <v>60.72</v>
       </c>
-      <c r="F61" s="30">
+      <c r="F61" s="31">
         <v>63.07</v>
       </c>
-      <c r="G61" s="30">
+      <c r="G61" s="31">
         <v>68.05</v>
       </c>
-      <c r="H61" s="31"/>
-      <c r="I61" s="31"/>
-      <c r="J61" s="31"/>
-      <c r="K61" s="31"/>
-      <c r="L61" s="31"/>
-      <c r="M61" s="31"/>
-      <c r="N61" s="31"/>
-      <c r="O61" s="31"/>
-      <c r="P61" s="31"/>
-      <c r="Q61" s="31"/>
-      <c r="R61" s="31"/>
-      <c r="S61" s="31"/>
-      <c r="T61" s="31"/>
-      <c r="U61" s="31"/>
-      <c r="V61" s="31"/>
-      <c r="W61" s="31"/>
-      <c r="X61" s="31"/>
-      <c r="Y61" s="31"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="32"/>
+      <c r="K61" s="32"/>
+      <c r="L61" s="32"/>
+      <c r="M61" s="32"/>
+      <c r="N61" s="32"/>
+      <c r="O61" s="32"/>
+      <c r="P61" s="32"/>
+      <c r="Q61" s="32"/>
+      <c r="R61" s="32"/>
+      <c r="S61" s="32"/>
+      <c r="T61" s="32"/>
+      <c r="U61" s="32"/>
+      <c r="V61" s="32"/>
+      <c r="W61" s="32"/>
+      <c r="X61" s="32"/>
+      <c r="Y61" s="32"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="28" t="s">
-        <v>373</v>
-      </c>
-      <c r="B62" s="30">
+      <c r="A62" s="29" t="s">
+        <v>374</v>
+      </c>
+      <c r="B62" s="31">
         <v>65.32</v>
       </c>
-      <c r="C62" s="30">
+      <c r="C62" s="31">
         <v>63.26</v>
       </c>
-      <c r="D62" s="30">
+      <c r="D62" s="31">
         <v>67.59</v>
       </c>
-      <c r="E62" s="30">
+      <c r="E62" s="31">
         <v>93.78</v>
       </c>
-      <c r="F62" s="30">
+      <c r="F62" s="31">
         <v>33.92</v>
       </c>
-      <c r="G62" s="31"/>
-      <c r="H62" s="31"/>
-      <c r="I62" s="31"/>
-      <c r="J62" s="31"/>
-      <c r="K62" s="31"/>
-      <c r="L62" s="31"/>
-      <c r="M62" s="31"/>
-      <c r="N62" s="31"/>
-      <c r="O62" s="31"/>
-      <c r="P62" s="31"/>
-      <c r="Q62" s="31"/>
-      <c r="R62" s="31"/>
-      <c r="S62" s="31"/>
-      <c r="T62" s="31"/>
-      <c r="U62" s="31"/>
-      <c r="V62" s="31"/>
-      <c r="W62" s="31"/>
-      <c r="X62" s="31"/>
-      <c r="Y62" s="31"/>
+      <c r="G62" s="32"/>
+      <c r="H62" s="32"/>
+      <c r="I62" s="32"/>
+      <c r="J62" s="32"/>
+      <c r="K62" s="32"/>
+      <c r="L62" s="32"/>
+      <c r="M62" s="32"/>
+      <c r="N62" s="32"/>
+      <c r="O62" s="32"/>
+      <c r="P62" s="32"/>
+      <c r="Q62" s="32"/>
+      <c r="R62" s="32"/>
+      <c r="S62" s="32"/>
+      <c r="T62" s="32"/>
+      <c r="U62" s="32"/>
+      <c r="V62" s="32"/>
+      <c r="W62" s="32"/>
+      <c r="X62" s="32"/>
+      <c r="Y62" s="32"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="26" t="s">
-        <v>374</v>
-      </c>
-      <c r="B63" s="27"/>
-      <c r="C63" s="27"/>
-      <c r="D63" s="27"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="27"/>
-      <c r="I63" s="27"/>
-      <c r="J63" s="27"/>
-      <c r="K63" s="27"/>
-      <c r="L63" s="27"/>
-      <c r="M63" s="27"/>
-      <c r="N63" s="27"/>
-      <c r="O63" s="27"/>
-      <c r="P63" s="27"/>
-      <c r="Q63" s="27"/>
-      <c r="R63" s="27"/>
-      <c r="S63" s="27"/>
-      <c r="T63" s="27"/>
-      <c r="U63" s="27"/>
-      <c r="V63" s="27"/>
-      <c r="W63" s="27"/>
-      <c r="X63" s="27"/>
-      <c r="Y63" s="27"/>
+      <c r="A63" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="B63" s="28"/>
+      <c r="C63" s="28"/>
+      <c r="D63" s="28"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
+      <c r="G63" s="28"/>
+      <c r="H63" s="28"/>
+      <c r="I63" s="28"/>
+      <c r="J63" s="28"/>
+      <c r="K63" s="28"/>
+      <c r="L63" s="28"/>
+      <c r="M63" s="28"/>
+      <c r="N63" s="28"/>
+      <c r="O63" s="28"/>
+      <c r="P63" s="28"/>
+      <c r="Q63" s="28"/>
+      <c r="R63" s="28"/>
+      <c r="S63" s="28"/>
+      <c r="T63" s="28"/>
+      <c r="U63" s="28"/>
+      <c r="V63" s="28"/>
+      <c r="W63" s="28"/>
+      <c r="X63" s="28"/>
+      <c r="Y63" s="28"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="28" t="s">
-        <v>375</v>
-      </c>
-      <c r="B64" s="31"/>
-      <c r="C64" s="29">
+      <c r="A64" s="29" t="s">
+        <v>376</v>
+      </c>
+      <c r="B64" s="32"/>
+      <c r="C64" s="30">
         <v>414.73</v>
       </c>
-      <c r="D64" s="30">
+      <c r="D64" s="31">
         <v>74.68</v>
       </c>
-      <c r="E64" s="30">
+      <c r="E64" s="31">
         <v>71.83</v>
       </c>
-      <c r="F64" s="30">
+      <c r="F64" s="31">
         <v>65.76</v>
       </c>
-      <c r="G64" s="29">
+      <c r="G64" s="30">
         <v>104.23</v>
       </c>
-      <c r="H64" s="31"/>
-      <c r="I64" s="31"/>
-      <c r="J64" s="31"/>
-      <c r="K64" s="31"/>
-      <c r="L64" s="31"/>
-      <c r="M64" s="31"/>
-      <c r="N64" s="31"/>
-      <c r="O64" s="31"/>
-      <c r="P64" s="31"/>
-      <c r="Q64" s="31"/>
-      <c r="R64" s="31"/>
-      <c r="S64" s="31"/>
-      <c r="T64" s="31"/>
-      <c r="U64" s="31"/>
-      <c r="V64" s="31"/>
-      <c r="W64" s="31"/>
-      <c r="X64" s="31"/>
-      <c r="Y64" s="31"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="32"/>
+      <c r="J64" s="32"/>
+      <c r="K64" s="32"/>
+      <c r="L64" s="32"/>
+      <c r="M64" s="32"/>
+      <c r="N64" s="32"/>
+      <c r="O64" s="32"/>
+      <c r="P64" s="32"/>
+      <c r="Q64" s="32"/>
+      <c r="R64" s="32"/>
+      <c r="S64" s="32"/>
+      <c r="T64" s="32"/>
+      <c r="U64" s="32"/>
+      <c r="V64" s="32"/>
+      <c r="W64" s="32"/>
+      <c r="X64" s="32"/>
+      <c r="Y64" s="32"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="28" t="s">
-        <v>376</v>
-      </c>
-      <c r="B65" s="30">
+      <c r="A65" s="29" t="s">
+        <v>377</v>
+      </c>
+      <c r="B65" s="31">
         <v>89.1</v>
       </c>
-      <c r="C65" s="30">
+      <c r="C65" s="31">
         <v>81.5</v>
       </c>
-      <c r="D65" s="30">
+      <c r="D65" s="31">
         <v>82.27</v>
       </c>
-      <c r="E65" s="29">
+      <c r="E65" s="30">
         <v>126.37</v>
       </c>
-      <c r="F65" s="30">
+      <c r="F65" s="31">
         <v>37.83</v>
       </c>
-      <c r="G65" s="31"/>
-      <c r="H65" s="31"/>
-      <c r="I65" s="31"/>
-      <c r="J65" s="31"/>
-      <c r="K65" s="31"/>
-      <c r="L65" s="31"/>
-      <c r="M65" s="31"/>
-      <c r="N65" s="31"/>
-      <c r="O65" s="31"/>
-      <c r="P65" s="31"/>
-      <c r="Q65" s="31"/>
-      <c r="R65" s="31"/>
-      <c r="S65" s="31"/>
-      <c r="T65" s="31"/>
-      <c r="U65" s="31"/>
-      <c r="V65" s="31"/>
-      <c r="W65" s="31"/>
-      <c r="X65" s="31"/>
-      <c r="Y65" s="31"/>
+      <c r="G65" s="32"/>
+      <c r="H65" s="32"/>
+      <c r="I65" s="32"/>
+      <c r="J65" s="32"/>
+      <c r="K65" s="32"/>
+      <c r="L65" s="32"/>
+      <c r="M65" s="32"/>
+      <c r="N65" s="32"/>
+      <c r="O65" s="32"/>
+      <c r="P65" s="32"/>
+      <c r="Q65" s="32"/>
+      <c r="R65" s="32"/>
+      <c r="S65" s="32"/>
+      <c r="T65" s="32"/>
+      <c r="U65" s="32"/>
+      <c r="V65" s="32"/>
+      <c r="W65" s="32"/>
+      <c r="X65" s="32"/>
+      <c r="Y65" s="32"/>
     </row>
     <row r="66" ht="15.75" customHeight="1"/>
     <row r="67" ht="15.75" customHeight="1"/>
